--- a/docs/tech/조직도 등록메뉴얼.xlsx
+++ b/docs/tech/조직도 등록메뉴얼.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="153222"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="21727"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\kaoni\jmocha\manual\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\JAVA\OPENSOLUTION\BASIC\EzFlowMasterOnlyPull\ezFlow4Java\docs\tech\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05101BA5-85C4-411B-9FE9-05B5F01215B2}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25200" windowHeight="11940"/>
+    <workbookView xWindow="28680" yWindow="15" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="작성시유의사항" sheetId="2" r:id="rId1"/>
@@ -17,12 +18,19 @@
     <sheet name="예시" sheetId="4" state="hidden" r:id="rId3"/>
     <sheet name="부서정보" sheetId="3" state="hidden" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="80">
   <si>
     <t>순서</t>
   </si>
@@ -311,21 +319,25 @@
   </si>
   <si>
     <t>① 모든 ID생성시 최소3자리 최대20자리의 글자수제한이 있다.</t>
+  </si>
+  <si>
+    <t>사번</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="000\-0000\-0000"/>
-    <numFmt numFmtId="165" formatCode="\1\900\-00\-00"/>
+    <numFmt numFmtId="176" formatCode="000\-0000\-0000"/>
+    <numFmt numFmtId="177" formatCode="\1\900\-00\-00"/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -333,7 +345,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -341,7 +353,7 @@
     <font>
       <sz val="18"/>
       <color theme="3"/>
-      <name val="Calibri Light"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="major"/>
@@ -350,7 +362,7 @@
       <b/>
       <sz val="15"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -359,7 +371,7 @@
       <b/>
       <sz val="13"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -368,7 +380,7 @@
       <b/>
       <sz val="11"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -376,7 +388,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -384,7 +396,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -392,7 +404,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -400,7 +412,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -409,7 +421,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -418,7 +430,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -426,7 +438,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -435,7 +447,7 @@
       <b/>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -443,7 +455,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -452,7 +464,7 @@
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -461,7 +473,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -469,14 +481,14 @@
     <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -484,7 +496,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -521,7 +533,7 @@
     <font>
       <sz val="15"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -529,7 +541,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -991,10 +1003,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
@@ -1107,7 +1119,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="그림 1"/>
+        <xdr:cNvPr id="2" name="그림 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
         </xdr:cNvPicPr>
@@ -1161,7 +1179,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="그림 2"/>
+        <xdr:cNvPr id="3" name="그림 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -1455,19 +1479,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B3:S42"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="4.28515625" style="10" customWidth="1"/>
-    <col min="2" max="2" width="12.28515625" style="10" customWidth="1"/>
-    <col min="3" max="3" width="11.140625" style="10" customWidth="1"/>
+    <col min="1" max="1" width="4.296875" style="10" customWidth="1"/>
+    <col min="2" max="2" width="12.296875" style="10" customWidth="1"/>
+    <col min="3" max="3" width="11.09765625" style="10" customWidth="1"/>
     <col min="4" max="8" width="9" style="10"/>
-    <col min="9" max="9" width="11.85546875" style="10" customWidth="1"/>
+    <col min="9" max="9" width="11.8984375" style="10" customWidth="1"/>
     <col min="10" max="16384" width="9" style="10"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:11" s="8" customFormat="1" ht="24">
+    <row r="3" spans="2:11" s="8" customFormat="1" ht="24" x14ac:dyDescent="0.4">
       <c r="B3" s="7" t="s">
         <v>58</v>
       </c>
@@ -1476,10 +1500,10 @@
       </c>
       <c r="K3" s="7"/>
     </row>
-    <row r="4" spans="2:11">
+    <row r="4" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B4" s="9"/>
     </row>
-    <row r="5" spans="2:11">
+    <row r="5" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B5" s="9" t="s">
         <v>72</v>
       </c>
@@ -1487,7 +1511,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="6" spans="2:11">
+    <row r="6" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B6" s="11" t="s">
         <v>73</v>
       </c>
@@ -1495,7 +1519,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="7" spans="2:11">
+    <row r="7" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B7" s="11" t="s">
         <v>74</v>
       </c>
@@ -1503,7 +1527,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="8" spans="2:11">
+    <row r="8" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B8" s="11" t="s">
         <v>59</v>
       </c>
@@ -1511,7 +1535,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="9" spans="2:11">
+    <row r="9" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B9" s="11" t="s">
         <v>75</v>
       </c>
@@ -1519,7 +1543,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="10" spans="2:11">
+    <row r="10" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B10" s="11" t="s">
         <v>76</v>
       </c>
@@ -1527,7 +1551,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="11" spans="2:11">
+    <row r="11" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B11" s="11" t="s">
         <v>60</v>
       </c>
@@ -1535,38 +1559,38 @@
         <v>66</v>
       </c>
     </row>
-    <row r="12" spans="2:11">
+    <row r="12" spans="2:11" x14ac:dyDescent="0.4">
       <c r="J12" s="10" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="13" spans="2:11">
+    <row r="13" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B13" s="11"/>
     </row>
-    <row r="14" spans="2:11">
+    <row r="14" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B14" s="11"/>
     </row>
-    <row r="15" spans="2:11">
+    <row r="15" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B15" s="11"/>
     </row>
-    <row r="18" spans="2:19" ht="24">
+    <row r="18" spans="2:19" ht="24" x14ac:dyDescent="0.4">
       <c r="S18" s="7"/>
     </row>
-    <row r="32" spans="2:19">
+    <row r="32" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B32" s="12"/>
     </row>
-    <row r="35" spans="2:3" hidden="1">
+    <row r="35" spans="2:3" hidden="1" x14ac:dyDescent="0.4">
       <c r="B35" s="14" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="36" spans="2:3" hidden="1">
+    <row r="36" spans="2:3" hidden="1" x14ac:dyDescent="0.4">
       <c r="B36" s="14" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="37" spans="2:3" hidden="1"/>
-    <row r="42" spans="2:3">
+    <row r="37" spans="2:3" hidden="1" x14ac:dyDescent="0.4"/>
+    <row r="42" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B42" s="13"/>
       <c r="C42" s="13"/>
     </row>
@@ -1579,23 +1603,23 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:Q2"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="3" max="3" width="13" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.09765625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.09765625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.42578125" customWidth="1"/>
-    <col min="13" max="13" width="11.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.3984375" customWidth="1"/>
+    <col min="14" max="14" width="11.09765625" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.3984375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.3984375" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1632,20 +1656,23 @@
       <c r="L1" t="s">
         <v>20</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" t="s">
+        <v>79</v>
+      </c>
+      <c r="N1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>11</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>12</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:16">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1657,15 +1684,15 @@
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <dataValidations count="3">
-    <dataValidation type="textLength" showInputMessage="1" showErrorMessage="1" prompt="회사ID 및 부서ID와 중복되지 않은 유일한것으로서 _x000a_3~9자리의 영문,숫자의 조합으로 만듭니다._x000a_" sqref="I337:I1048576 I1 I2:I336">
+    <dataValidation type="textLength" showInputMessage="1" showErrorMessage="1" prompt="회사ID 및 부서ID와 중복되지 않은 유일한것으로서 _x000a_3~9자리의 영문,숫자의 조합으로 만듭니다._x000a_" sqref="I1:I1048576" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>3</formula1>
       <formula2>9</formula2>
     </dataValidation>
-    <dataValidation type="textLength" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E10 D1 D2:D288 F1 F2:F372">
+    <dataValidation type="textLength" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E10 D1:D288 F1:F372" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>3</formula1>
       <formula2>9</formula2>
     </dataValidation>
-    <dataValidation type="textLength" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="8~12자리의영문,숫자,특수문자의 조합으로 생성합니다." sqref="L1:L1048576">
+    <dataValidation type="textLength" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="8~12자리의영문,숫자,특수문자의 조합으로 생성합니다." sqref="L1:L1048576" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>8</formula1>
       <formula2>12</formula2>
     </dataValidation>
@@ -1675,11 +1702,11 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000003000000}">
           <x14:formula1>
             <xm:f>작성시유의사항!$B$35:$B$36</xm:f>
           </x14:formula1>
-          <xm:sqref>N1:N1048576</xm:sqref>
+          <xm:sqref>O1:O1048576</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1688,23 +1715,23 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:O10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="3" max="3" width="13" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.09765625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.09765625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.42578125" customWidth="1"/>
-    <col min="12" max="12" width="11.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.3984375" customWidth="1"/>
+    <col min="12" max="12" width="11.09765625" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.3984375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.3984375" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1751,7 +1778,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1772,7 +1799,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1793,7 +1820,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1814,7 +1841,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1835,7 +1862,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1856,7 +1883,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1895,7 +1922,7 @@
         <v>1056235623</v>
       </c>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1934,7 +1961,7 @@
         <v>1089568956</v>
       </c>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1973,7 +2000,7 @@
         <v>1045124512</v>
       </c>
     </row>
-    <row r="10" spans="1:15">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2015,18 +2042,18 @@
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <dataValidations xWindow="788" yWindow="443" count="4">
-    <dataValidation type="textLength" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E10 F1:F10 F12 D1:D10 D12">
+    <dataValidation type="textLength" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E10 F1:F10 F12 D1:D10 D12" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>3</formula1>
       <formula2>9</formula2>
     </dataValidation>
-    <dataValidation type="textLength" showInputMessage="1" showErrorMessage="1" prompt="회사ID 및 부서ID와 중복되지 않은 유일한것으로서 _x000a_3~9자리의 영문,숫자의 조합으로 만듭니다._x000a_" sqref="I1:I10 I12:I1048576">
+    <dataValidation type="textLength" showInputMessage="1" showErrorMessage="1" prompt="회사ID 및 부서ID와 중복되지 않은 유일한것으로서 _x000a_3~9자리의 영문,숫자의 조합으로 만듭니다._x000a_" sqref="I1:I10 I12:I1048576" xr:uid="{00000000-0002-0000-0200-000001000000}">
       <formula1>3</formula1>
       <formula2>9</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M12">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M12" xr:uid="{00000000-0002-0000-0200-000002000000}">
       <formula1>$U$32:$U$33</formula1>
     </dataValidation>
-    <dataValidation type="textLength" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="8~12자리의영문,숫자,특수문자의 조합으로 생성합니다." sqref="K1:K1048576">
+    <dataValidation type="textLength" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="8~12자리의영문,숫자,특수문자의 조합으로 생성합니다." sqref="K1:K1048576" xr:uid="{00000000-0002-0000-0200-000003000000}">
       <formula1>8</formula1>
       <formula2>12</formula2>
     </dataValidation>
@@ -2036,13 +2063,13 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xWindow="788" yWindow="443" count="2">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0200-000004000000}">
           <x14:formula1>
             <xm:f>작성시유의사항!$U$32:$U$33</xm:f>
           </x14:formula1>
           <xm:sqref>M2:M10</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0200-000005000000}">
           <x14:formula1>
             <xm:f>작성시유의사항!$B$35:$B$36</xm:f>
           </x14:formula1>
@@ -2055,334 +2082,334 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:E32"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
-    <col min="2" max="2" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.85546875" style="3" customWidth="1"/>
-    <col min="4" max="4" width="16.42578125" style="3" customWidth="1"/>
-    <col min="5" max="5" width="19.7109375" style="3" customWidth="1"/>
+    <col min="2" max="2" width="21.296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.8984375" style="3" customWidth="1"/>
+    <col min="4" max="4" width="16.3984375" style="3" customWidth="1"/>
+    <col min="5" max="5" width="19.69921875" style="3" customWidth="1"/>
     <col min="6" max="257" width="9" style="3"/>
-    <col min="258" max="258" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="259" max="259" width="14.85546875" style="3" customWidth="1"/>
-    <col min="260" max="260" width="16.42578125" style="3" customWidth="1"/>
-    <col min="261" max="261" width="19.7109375" style="3" customWidth="1"/>
+    <col min="258" max="258" width="21.296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="259" max="259" width="14.8984375" style="3" customWidth="1"/>
+    <col min="260" max="260" width="16.3984375" style="3" customWidth="1"/>
+    <col min="261" max="261" width="19.69921875" style="3" customWidth="1"/>
     <col min="262" max="513" width="9" style="3"/>
-    <col min="514" max="514" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="515" max="515" width="14.85546875" style="3" customWidth="1"/>
-    <col min="516" max="516" width="16.42578125" style="3" customWidth="1"/>
-    <col min="517" max="517" width="19.7109375" style="3" customWidth="1"/>
+    <col min="514" max="514" width="21.296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="515" max="515" width="14.8984375" style="3" customWidth="1"/>
+    <col min="516" max="516" width="16.3984375" style="3" customWidth="1"/>
+    <col min="517" max="517" width="19.69921875" style="3" customWidth="1"/>
     <col min="518" max="769" width="9" style="3"/>
-    <col min="770" max="770" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="771" max="771" width="14.85546875" style="3" customWidth="1"/>
-    <col min="772" max="772" width="16.42578125" style="3" customWidth="1"/>
-    <col min="773" max="773" width="19.7109375" style="3" customWidth="1"/>
+    <col min="770" max="770" width="21.296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="771" max="771" width="14.8984375" style="3" customWidth="1"/>
+    <col min="772" max="772" width="16.3984375" style="3" customWidth="1"/>
+    <col min="773" max="773" width="19.69921875" style="3" customWidth="1"/>
     <col min="774" max="1025" width="9" style="3"/>
-    <col min="1026" max="1026" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="1027" max="1027" width="14.85546875" style="3" customWidth="1"/>
-    <col min="1028" max="1028" width="16.42578125" style="3" customWidth="1"/>
-    <col min="1029" max="1029" width="19.7109375" style="3" customWidth="1"/>
+    <col min="1026" max="1026" width="21.296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="1027" max="1027" width="14.8984375" style="3" customWidth="1"/>
+    <col min="1028" max="1028" width="16.3984375" style="3" customWidth="1"/>
+    <col min="1029" max="1029" width="19.69921875" style="3" customWidth="1"/>
     <col min="1030" max="1281" width="9" style="3"/>
-    <col min="1282" max="1282" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="1283" max="1283" width="14.85546875" style="3" customWidth="1"/>
-    <col min="1284" max="1284" width="16.42578125" style="3" customWidth="1"/>
-    <col min="1285" max="1285" width="19.7109375" style="3" customWidth="1"/>
+    <col min="1282" max="1282" width="21.296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="1283" max="1283" width="14.8984375" style="3" customWidth="1"/>
+    <col min="1284" max="1284" width="16.3984375" style="3" customWidth="1"/>
+    <col min="1285" max="1285" width="19.69921875" style="3" customWidth="1"/>
     <col min="1286" max="1537" width="9" style="3"/>
-    <col min="1538" max="1538" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="1539" max="1539" width="14.85546875" style="3" customWidth="1"/>
-    <col min="1540" max="1540" width="16.42578125" style="3" customWidth="1"/>
-    <col min="1541" max="1541" width="19.7109375" style="3" customWidth="1"/>
+    <col min="1538" max="1538" width="21.296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="1539" max="1539" width="14.8984375" style="3" customWidth="1"/>
+    <col min="1540" max="1540" width="16.3984375" style="3" customWidth="1"/>
+    <col min="1541" max="1541" width="19.69921875" style="3" customWidth="1"/>
     <col min="1542" max="1793" width="9" style="3"/>
-    <col min="1794" max="1794" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="1795" max="1795" width="14.85546875" style="3" customWidth="1"/>
-    <col min="1796" max="1796" width="16.42578125" style="3" customWidth="1"/>
-    <col min="1797" max="1797" width="19.7109375" style="3" customWidth="1"/>
+    <col min="1794" max="1794" width="21.296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="1795" max="1795" width="14.8984375" style="3" customWidth="1"/>
+    <col min="1796" max="1796" width="16.3984375" style="3" customWidth="1"/>
+    <col min="1797" max="1797" width="19.69921875" style="3" customWidth="1"/>
     <col min="1798" max="2049" width="9" style="3"/>
-    <col min="2050" max="2050" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="2051" max="2051" width="14.85546875" style="3" customWidth="1"/>
-    <col min="2052" max="2052" width="16.42578125" style="3" customWidth="1"/>
-    <col min="2053" max="2053" width="19.7109375" style="3" customWidth="1"/>
+    <col min="2050" max="2050" width="21.296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="2051" max="2051" width="14.8984375" style="3" customWidth="1"/>
+    <col min="2052" max="2052" width="16.3984375" style="3" customWidth="1"/>
+    <col min="2053" max="2053" width="19.69921875" style="3" customWidth="1"/>
     <col min="2054" max="2305" width="9" style="3"/>
-    <col min="2306" max="2306" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="2307" max="2307" width="14.85546875" style="3" customWidth="1"/>
-    <col min="2308" max="2308" width="16.42578125" style="3" customWidth="1"/>
-    <col min="2309" max="2309" width="19.7109375" style="3" customWidth="1"/>
+    <col min="2306" max="2306" width="21.296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="2307" max="2307" width="14.8984375" style="3" customWidth="1"/>
+    <col min="2308" max="2308" width="16.3984375" style="3" customWidth="1"/>
+    <col min="2309" max="2309" width="19.69921875" style="3" customWidth="1"/>
     <col min="2310" max="2561" width="9" style="3"/>
-    <col min="2562" max="2562" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="2563" max="2563" width="14.85546875" style="3" customWidth="1"/>
-    <col min="2564" max="2564" width="16.42578125" style="3" customWidth="1"/>
-    <col min="2565" max="2565" width="19.7109375" style="3" customWidth="1"/>
+    <col min="2562" max="2562" width="21.296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="2563" max="2563" width="14.8984375" style="3" customWidth="1"/>
+    <col min="2564" max="2564" width="16.3984375" style="3" customWidth="1"/>
+    <col min="2565" max="2565" width="19.69921875" style="3" customWidth="1"/>
     <col min="2566" max="2817" width="9" style="3"/>
-    <col min="2818" max="2818" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="2819" max="2819" width="14.85546875" style="3" customWidth="1"/>
-    <col min="2820" max="2820" width="16.42578125" style="3" customWidth="1"/>
-    <col min="2821" max="2821" width="19.7109375" style="3" customWidth="1"/>
+    <col min="2818" max="2818" width="21.296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="2819" max="2819" width="14.8984375" style="3" customWidth="1"/>
+    <col min="2820" max="2820" width="16.3984375" style="3" customWidth="1"/>
+    <col min="2821" max="2821" width="19.69921875" style="3" customWidth="1"/>
     <col min="2822" max="3073" width="9" style="3"/>
-    <col min="3074" max="3074" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="3075" max="3075" width="14.85546875" style="3" customWidth="1"/>
-    <col min="3076" max="3076" width="16.42578125" style="3" customWidth="1"/>
-    <col min="3077" max="3077" width="19.7109375" style="3" customWidth="1"/>
+    <col min="3074" max="3074" width="21.296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="3075" max="3075" width="14.8984375" style="3" customWidth="1"/>
+    <col min="3076" max="3076" width="16.3984375" style="3" customWidth="1"/>
+    <col min="3077" max="3077" width="19.69921875" style="3" customWidth="1"/>
     <col min="3078" max="3329" width="9" style="3"/>
-    <col min="3330" max="3330" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="3331" max="3331" width="14.85546875" style="3" customWidth="1"/>
-    <col min="3332" max="3332" width="16.42578125" style="3" customWidth="1"/>
-    <col min="3333" max="3333" width="19.7109375" style="3" customWidth="1"/>
+    <col min="3330" max="3330" width="21.296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="3331" max="3331" width="14.8984375" style="3" customWidth="1"/>
+    <col min="3332" max="3332" width="16.3984375" style="3" customWidth="1"/>
+    <col min="3333" max="3333" width="19.69921875" style="3" customWidth="1"/>
     <col min="3334" max="3585" width="9" style="3"/>
-    <col min="3586" max="3586" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="3587" max="3587" width="14.85546875" style="3" customWidth="1"/>
-    <col min="3588" max="3588" width="16.42578125" style="3" customWidth="1"/>
-    <col min="3589" max="3589" width="19.7109375" style="3" customWidth="1"/>
+    <col min="3586" max="3586" width="21.296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="3587" max="3587" width="14.8984375" style="3" customWidth="1"/>
+    <col min="3588" max="3588" width="16.3984375" style="3" customWidth="1"/>
+    <col min="3589" max="3589" width="19.69921875" style="3" customWidth="1"/>
     <col min="3590" max="3841" width="9" style="3"/>
-    <col min="3842" max="3842" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="3843" max="3843" width="14.85546875" style="3" customWidth="1"/>
-    <col min="3844" max="3844" width="16.42578125" style="3" customWidth="1"/>
-    <col min="3845" max="3845" width="19.7109375" style="3" customWidth="1"/>
+    <col min="3842" max="3842" width="21.296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="3843" max="3843" width="14.8984375" style="3" customWidth="1"/>
+    <col min="3844" max="3844" width="16.3984375" style="3" customWidth="1"/>
+    <col min="3845" max="3845" width="19.69921875" style="3" customWidth="1"/>
     <col min="3846" max="4097" width="9" style="3"/>
-    <col min="4098" max="4098" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="4099" max="4099" width="14.85546875" style="3" customWidth="1"/>
-    <col min="4100" max="4100" width="16.42578125" style="3" customWidth="1"/>
-    <col min="4101" max="4101" width="19.7109375" style="3" customWidth="1"/>
+    <col min="4098" max="4098" width="21.296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="4099" max="4099" width="14.8984375" style="3" customWidth="1"/>
+    <col min="4100" max="4100" width="16.3984375" style="3" customWidth="1"/>
+    <col min="4101" max="4101" width="19.69921875" style="3" customWidth="1"/>
     <col min="4102" max="4353" width="9" style="3"/>
-    <col min="4354" max="4354" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="4355" max="4355" width="14.85546875" style="3" customWidth="1"/>
-    <col min="4356" max="4356" width="16.42578125" style="3" customWidth="1"/>
-    <col min="4357" max="4357" width="19.7109375" style="3" customWidth="1"/>
+    <col min="4354" max="4354" width="21.296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="4355" max="4355" width="14.8984375" style="3" customWidth="1"/>
+    <col min="4356" max="4356" width="16.3984375" style="3" customWidth="1"/>
+    <col min="4357" max="4357" width="19.69921875" style="3" customWidth="1"/>
     <col min="4358" max="4609" width="9" style="3"/>
-    <col min="4610" max="4610" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="4611" max="4611" width="14.85546875" style="3" customWidth="1"/>
-    <col min="4612" max="4612" width="16.42578125" style="3" customWidth="1"/>
-    <col min="4613" max="4613" width="19.7109375" style="3" customWidth="1"/>
+    <col min="4610" max="4610" width="21.296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="4611" max="4611" width="14.8984375" style="3" customWidth="1"/>
+    <col min="4612" max="4612" width="16.3984375" style="3" customWidth="1"/>
+    <col min="4613" max="4613" width="19.69921875" style="3" customWidth="1"/>
     <col min="4614" max="4865" width="9" style="3"/>
-    <col min="4866" max="4866" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="4867" max="4867" width="14.85546875" style="3" customWidth="1"/>
-    <col min="4868" max="4868" width="16.42578125" style="3" customWidth="1"/>
-    <col min="4869" max="4869" width="19.7109375" style="3" customWidth="1"/>
+    <col min="4866" max="4866" width="21.296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="4867" max="4867" width="14.8984375" style="3" customWidth="1"/>
+    <col min="4868" max="4868" width="16.3984375" style="3" customWidth="1"/>
+    <col min="4869" max="4869" width="19.69921875" style="3" customWidth="1"/>
     <col min="4870" max="5121" width="9" style="3"/>
-    <col min="5122" max="5122" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="5123" max="5123" width="14.85546875" style="3" customWidth="1"/>
-    <col min="5124" max="5124" width="16.42578125" style="3" customWidth="1"/>
-    <col min="5125" max="5125" width="19.7109375" style="3" customWidth="1"/>
+    <col min="5122" max="5122" width="21.296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="5123" max="5123" width="14.8984375" style="3" customWidth="1"/>
+    <col min="5124" max="5124" width="16.3984375" style="3" customWidth="1"/>
+    <col min="5125" max="5125" width="19.69921875" style="3" customWidth="1"/>
     <col min="5126" max="5377" width="9" style="3"/>
-    <col min="5378" max="5378" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="5379" max="5379" width="14.85546875" style="3" customWidth="1"/>
-    <col min="5380" max="5380" width="16.42578125" style="3" customWidth="1"/>
-    <col min="5381" max="5381" width="19.7109375" style="3" customWidth="1"/>
+    <col min="5378" max="5378" width="21.296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="5379" max="5379" width="14.8984375" style="3" customWidth="1"/>
+    <col min="5380" max="5380" width="16.3984375" style="3" customWidth="1"/>
+    <col min="5381" max="5381" width="19.69921875" style="3" customWidth="1"/>
     <col min="5382" max="5633" width="9" style="3"/>
-    <col min="5634" max="5634" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="5635" max="5635" width="14.85546875" style="3" customWidth="1"/>
-    <col min="5636" max="5636" width="16.42578125" style="3" customWidth="1"/>
-    <col min="5637" max="5637" width="19.7109375" style="3" customWidth="1"/>
+    <col min="5634" max="5634" width="21.296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="5635" max="5635" width="14.8984375" style="3" customWidth="1"/>
+    <col min="5636" max="5636" width="16.3984375" style="3" customWidth="1"/>
+    <col min="5637" max="5637" width="19.69921875" style="3" customWidth="1"/>
     <col min="5638" max="5889" width="9" style="3"/>
-    <col min="5890" max="5890" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="5891" max="5891" width="14.85546875" style="3" customWidth="1"/>
-    <col min="5892" max="5892" width="16.42578125" style="3" customWidth="1"/>
-    <col min="5893" max="5893" width="19.7109375" style="3" customWidth="1"/>
+    <col min="5890" max="5890" width="21.296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="5891" max="5891" width="14.8984375" style="3" customWidth="1"/>
+    <col min="5892" max="5892" width="16.3984375" style="3" customWidth="1"/>
+    <col min="5893" max="5893" width="19.69921875" style="3" customWidth="1"/>
     <col min="5894" max="6145" width="9" style="3"/>
-    <col min="6146" max="6146" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="6147" max="6147" width="14.85546875" style="3" customWidth="1"/>
-    <col min="6148" max="6148" width="16.42578125" style="3" customWidth="1"/>
-    <col min="6149" max="6149" width="19.7109375" style="3" customWidth="1"/>
+    <col min="6146" max="6146" width="21.296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="6147" max="6147" width="14.8984375" style="3" customWidth="1"/>
+    <col min="6148" max="6148" width="16.3984375" style="3" customWidth="1"/>
+    <col min="6149" max="6149" width="19.69921875" style="3" customWidth="1"/>
     <col min="6150" max="6401" width="9" style="3"/>
-    <col min="6402" max="6402" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="6403" max="6403" width="14.85546875" style="3" customWidth="1"/>
-    <col min="6404" max="6404" width="16.42578125" style="3" customWidth="1"/>
-    <col min="6405" max="6405" width="19.7109375" style="3" customWidth="1"/>
+    <col min="6402" max="6402" width="21.296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="6403" max="6403" width="14.8984375" style="3" customWidth="1"/>
+    <col min="6404" max="6404" width="16.3984375" style="3" customWidth="1"/>
+    <col min="6405" max="6405" width="19.69921875" style="3" customWidth="1"/>
     <col min="6406" max="6657" width="9" style="3"/>
-    <col min="6658" max="6658" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="6659" max="6659" width="14.85546875" style="3" customWidth="1"/>
-    <col min="6660" max="6660" width="16.42578125" style="3" customWidth="1"/>
-    <col min="6661" max="6661" width="19.7109375" style="3" customWidth="1"/>
+    <col min="6658" max="6658" width="21.296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="6659" max="6659" width="14.8984375" style="3" customWidth="1"/>
+    <col min="6660" max="6660" width="16.3984375" style="3" customWidth="1"/>
+    <col min="6661" max="6661" width="19.69921875" style="3" customWidth="1"/>
     <col min="6662" max="6913" width="9" style="3"/>
-    <col min="6914" max="6914" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="6915" max="6915" width="14.85546875" style="3" customWidth="1"/>
-    <col min="6916" max="6916" width="16.42578125" style="3" customWidth="1"/>
-    <col min="6917" max="6917" width="19.7109375" style="3" customWidth="1"/>
+    <col min="6914" max="6914" width="21.296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="6915" max="6915" width="14.8984375" style="3" customWidth="1"/>
+    <col min="6916" max="6916" width="16.3984375" style="3" customWidth="1"/>
+    <col min="6917" max="6917" width="19.69921875" style="3" customWidth="1"/>
     <col min="6918" max="7169" width="9" style="3"/>
-    <col min="7170" max="7170" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="7171" max="7171" width="14.85546875" style="3" customWidth="1"/>
-    <col min="7172" max="7172" width="16.42578125" style="3" customWidth="1"/>
-    <col min="7173" max="7173" width="19.7109375" style="3" customWidth="1"/>
+    <col min="7170" max="7170" width="21.296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="7171" max="7171" width="14.8984375" style="3" customWidth="1"/>
+    <col min="7172" max="7172" width="16.3984375" style="3" customWidth="1"/>
+    <col min="7173" max="7173" width="19.69921875" style="3" customWidth="1"/>
     <col min="7174" max="7425" width="9" style="3"/>
-    <col min="7426" max="7426" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="7427" max="7427" width="14.85546875" style="3" customWidth="1"/>
-    <col min="7428" max="7428" width="16.42578125" style="3" customWidth="1"/>
-    <col min="7429" max="7429" width="19.7109375" style="3" customWidth="1"/>
+    <col min="7426" max="7426" width="21.296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="7427" max="7427" width="14.8984375" style="3" customWidth="1"/>
+    <col min="7428" max="7428" width="16.3984375" style="3" customWidth="1"/>
+    <col min="7429" max="7429" width="19.69921875" style="3" customWidth="1"/>
     <col min="7430" max="7681" width="9" style="3"/>
-    <col min="7682" max="7682" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="7683" max="7683" width="14.85546875" style="3" customWidth="1"/>
-    <col min="7684" max="7684" width="16.42578125" style="3" customWidth="1"/>
-    <col min="7685" max="7685" width="19.7109375" style="3" customWidth="1"/>
+    <col min="7682" max="7682" width="21.296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="7683" max="7683" width="14.8984375" style="3" customWidth="1"/>
+    <col min="7684" max="7684" width="16.3984375" style="3" customWidth="1"/>
+    <col min="7685" max="7685" width="19.69921875" style="3" customWidth="1"/>
     <col min="7686" max="7937" width="9" style="3"/>
-    <col min="7938" max="7938" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="7939" max="7939" width="14.85546875" style="3" customWidth="1"/>
-    <col min="7940" max="7940" width="16.42578125" style="3" customWidth="1"/>
-    <col min="7941" max="7941" width="19.7109375" style="3" customWidth="1"/>
+    <col min="7938" max="7938" width="21.296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="7939" max="7939" width="14.8984375" style="3" customWidth="1"/>
+    <col min="7940" max="7940" width="16.3984375" style="3" customWidth="1"/>
+    <col min="7941" max="7941" width="19.69921875" style="3" customWidth="1"/>
     <col min="7942" max="8193" width="9" style="3"/>
-    <col min="8194" max="8194" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="8195" max="8195" width="14.85546875" style="3" customWidth="1"/>
-    <col min="8196" max="8196" width="16.42578125" style="3" customWidth="1"/>
-    <col min="8197" max="8197" width="19.7109375" style="3" customWidth="1"/>
+    <col min="8194" max="8194" width="21.296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="8195" max="8195" width="14.8984375" style="3" customWidth="1"/>
+    <col min="8196" max="8196" width="16.3984375" style="3" customWidth="1"/>
+    <col min="8197" max="8197" width="19.69921875" style="3" customWidth="1"/>
     <col min="8198" max="8449" width="9" style="3"/>
-    <col min="8450" max="8450" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="8451" max="8451" width="14.85546875" style="3" customWidth="1"/>
-    <col min="8452" max="8452" width="16.42578125" style="3" customWidth="1"/>
-    <col min="8453" max="8453" width="19.7109375" style="3" customWidth="1"/>
+    <col min="8450" max="8450" width="21.296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="8451" max="8451" width="14.8984375" style="3" customWidth="1"/>
+    <col min="8452" max="8452" width="16.3984375" style="3" customWidth="1"/>
+    <col min="8453" max="8453" width="19.69921875" style="3" customWidth="1"/>
     <col min="8454" max="8705" width="9" style="3"/>
-    <col min="8706" max="8706" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="8707" max="8707" width="14.85546875" style="3" customWidth="1"/>
-    <col min="8708" max="8708" width="16.42578125" style="3" customWidth="1"/>
-    <col min="8709" max="8709" width="19.7109375" style="3" customWidth="1"/>
+    <col min="8706" max="8706" width="21.296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="8707" max="8707" width="14.8984375" style="3" customWidth="1"/>
+    <col min="8708" max="8708" width="16.3984375" style="3" customWidth="1"/>
+    <col min="8709" max="8709" width="19.69921875" style="3" customWidth="1"/>
     <col min="8710" max="8961" width="9" style="3"/>
-    <col min="8962" max="8962" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="8963" max="8963" width="14.85546875" style="3" customWidth="1"/>
-    <col min="8964" max="8964" width="16.42578125" style="3" customWidth="1"/>
-    <col min="8965" max="8965" width="19.7109375" style="3" customWidth="1"/>
+    <col min="8962" max="8962" width="21.296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="8963" max="8963" width="14.8984375" style="3" customWidth="1"/>
+    <col min="8964" max="8964" width="16.3984375" style="3" customWidth="1"/>
+    <col min="8965" max="8965" width="19.69921875" style="3" customWidth="1"/>
     <col min="8966" max="9217" width="9" style="3"/>
-    <col min="9218" max="9218" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="9219" max="9219" width="14.85546875" style="3" customWidth="1"/>
-    <col min="9220" max="9220" width="16.42578125" style="3" customWidth="1"/>
-    <col min="9221" max="9221" width="19.7109375" style="3" customWidth="1"/>
+    <col min="9218" max="9218" width="21.296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="9219" max="9219" width="14.8984375" style="3" customWidth="1"/>
+    <col min="9220" max="9220" width="16.3984375" style="3" customWidth="1"/>
+    <col min="9221" max="9221" width="19.69921875" style="3" customWidth="1"/>
     <col min="9222" max="9473" width="9" style="3"/>
-    <col min="9474" max="9474" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="9475" max="9475" width="14.85546875" style="3" customWidth="1"/>
-    <col min="9476" max="9476" width="16.42578125" style="3" customWidth="1"/>
-    <col min="9477" max="9477" width="19.7109375" style="3" customWidth="1"/>
+    <col min="9474" max="9474" width="21.296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="9475" max="9475" width="14.8984375" style="3" customWidth="1"/>
+    <col min="9476" max="9476" width="16.3984375" style="3" customWidth="1"/>
+    <col min="9477" max="9477" width="19.69921875" style="3" customWidth="1"/>
     <col min="9478" max="9729" width="9" style="3"/>
-    <col min="9730" max="9730" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="9731" max="9731" width="14.85546875" style="3" customWidth="1"/>
-    <col min="9732" max="9732" width="16.42578125" style="3" customWidth="1"/>
-    <col min="9733" max="9733" width="19.7109375" style="3" customWidth="1"/>
+    <col min="9730" max="9730" width="21.296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="9731" max="9731" width="14.8984375" style="3" customWidth="1"/>
+    <col min="9732" max="9732" width="16.3984375" style="3" customWidth="1"/>
+    <col min="9733" max="9733" width="19.69921875" style="3" customWidth="1"/>
     <col min="9734" max="9985" width="9" style="3"/>
-    <col min="9986" max="9986" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="9987" max="9987" width="14.85546875" style="3" customWidth="1"/>
-    <col min="9988" max="9988" width="16.42578125" style="3" customWidth="1"/>
-    <col min="9989" max="9989" width="19.7109375" style="3" customWidth="1"/>
+    <col min="9986" max="9986" width="21.296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="9987" max="9987" width="14.8984375" style="3" customWidth="1"/>
+    <col min="9988" max="9988" width="16.3984375" style="3" customWidth="1"/>
+    <col min="9989" max="9989" width="19.69921875" style="3" customWidth="1"/>
     <col min="9990" max="10241" width="9" style="3"/>
-    <col min="10242" max="10242" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="10243" max="10243" width="14.85546875" style="3" customWidth="1"/>
-    <col min="10244" max="10244" width="16.42578125" style="3" customWidth="1"/>
-    <col min="10245" max="10245" width="19.7109375" style="3" customWidth="1"/>
+    <col min="10242" max="10242" width="21.296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="10243" max="10243" width="14.8984375" style="3" customWidth="1"/>
+    <col min="10244" max="10244" width="16.3984375" style="3" customWidth="1"/>
+    <col min="10245" max="10245" width="19.69921875" style="3" customWidth="1"/>
     <col min="10246" max="10497" width="9" style="3"/>
-    <col min="10498" max="10498" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="10499" max="10499" width="14.85546875" style="3" customWidth="1"/>
-    <col min="10500" max="10500" width="16.42578125" style="3" customWidth="1"/>
-    <col min="10501" max="10501" width="19.7109375" style="3" customWidth="1"/>
+    <col min="10498" max="10498" width="21.296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="10499" max="10499" width="14.8984375" style="3" customWidth="1"/>
+    <col min="10500" max="10500" width="16.3984375" style="3" customWidth="1"/>
+    <col min="10501" max="10501" width="19.69921875" style="3" customWidth="1"/>
     <col min="10502" max="10753" width="9" style="3"/>
-    <col min="10754" max="10754" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="10755" max="10755" width="14.85546875" style="3" customWidth="1"/>
-    <col min="10756" max="10756" width="16.42578125" style="3" customWidth="1"/>
-    <col min="10757" max="10757" width="19.7109375" style="3" customWidth="1"/>
+    <col min="10754" max="10754" width="21.296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="10755" max="10755" width="14.8984375" style="3" customWidth="1"/>
+    <col min="10756" max="10756" width="16.3984375" style="3" customWidth="1"/>
+    <col min="10757" max="10757" width="19.69921875" style="3" customWidth="1"/>
     <col min="10758" max="11009" width="9" style="3"/>
-    <col min="11010" max="11010" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="11011" max="11011" width="14.85546875" style="3" customWidth="1"/>
-    <col min="11012" max="11012" width="16.42578125" style="3" customWidth="1"/>
-    <col min="11013" max="11013" width="19.7109375" style="3" customWidth="1"/>
+    <col min="11010" max="11010" width="21.296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="11011" max="11011" width="14.8984375" style="3" customWidth="1"/>
+    <col min="11012" max="11012" width="16.3984375" style="3" customWidth="1"/>
+    <col min="11013" max="11013" width="19.69921875" style="3" customWidth="1"/>
     <col min="11014" max="11265" width="9" style="3"/>
-    <col min="11266" max="11266" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="11267" max="11267" width="14.85546875" style="3" customWidth="1"/>
-    <col min="11268" max="11268" width="16.42578125" style="3" customWidth="1"/>
-    <col min="11269" max="11269" width="19.7109375" style="3" customWidth="1"/>
+    <col min="11266" max="11266" width="21.296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="11267" max="11267" width="14.8984375" style="3" customWidth="1"/>
+    <col min="11268" max="11268" width="16.3984375" style="3" customWidth="1"/>
+    <col min="11269" max="11269" width="19.69921875" style="3" customWidth="1"/>
     <col min="11270" max="11521" width="9" style="3"/>
-    <col min="11522" max="11522" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="11523" max="11523" width="14.85546875" style="3" customWidth="1"/>
-    <col min="11524" max="11524" width="16.42578125" style="3" customWidth="1"/>
-    <col min="11525" max="11525" width="19.7109375" style="3" customWidth="1"/>
+    <col min="11522" max="11522" width="21.296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="11523" max="11523" width="14.8984375" style="3" customWidth="1"/>
+    <col min="11524" max="11524" width="16.3984375" style="3" customWidth="1"/>
+    <col min="11525" max="11525" width="19.69921875" style="3" customWidth="1"/>
     <col min="11526" max="11777" width="9" style="3"/>
-    <col min="11778" max="11778" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="11779" max="11779" width="14.85546875" style="3" customWidth="1"/>
-    <col min="11780" max="11780" width="16.42578125" style="3" customWidth="1"/>
-    <col min="11781" max="11781" width="19.7109375" style="3" customWidth="1"/>
+    <col min="11778" max="11778" width="21.296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="11779" max="11779" width="14.8984375" style="3" customWidth="1"/>
+    <col min="11780" max="11780" width="16.3984375" style="3" customWidth="1"/>
+    <col min="11781" max="11781" width="19.69921875" style="3" customWidth="1"/>
     <col min="11782" max="12033" width="9" style="3"/>
-    <col min="12034" max="12034" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="12035" max="12035" width="14.85546875" style="3" customWidth="1"/>
-    <col min="12036" max="12036" width="16.42578125" style="3" customWidth="1"/>
-    <col min="12037" max="12037" width="19.7109375" style="3" customWidth="1"/>
+    <col min="12034" max="12034" width="21.296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="12035" max="12035" width="14.8984375" style="3" customWidth="1"/>
+    <col min="12036" max="12036" width="16.3984375" style="3" customWidth="1"/>
+    <col min="12037" max="12037" width="19.69921875" style="3" customWidth="1"/>
     <col min="12038" max="12289" width="9" style="3"/>
-    <col min="12290" max="12290" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="12291" max="12291" width="14.85546875" style="3" customWidth="1"/>
-    <col min="12292" max="12292" width="16.42578125" style="3" customWidth="1"/>
-    <col min="12293" max="12293" width="19.7109375" style="3" customWidth="1"/>
+    <col min="12290" max="12290" width="21.296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="12291" max="12291" width="14.8984375" style="3" customWidth="1"/>
+    <col min="12292" max="12292" width="16.3984375" style="3" customWidth="1"/>
+    <col min="12293" max="12293" width="19.69921875" style="3" customWidth="1"/>
     <col min="12294" max="12545" width="9" style="3"/>
-    <col min="12546" max="12546" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="12547" max="12547" width="14.85546875" style="3" customWidth="1"/>
-    <col min="12548" max="12548" width="16.42578125" style="3" customWidth="1"/>
-    <col min="12549" max="12549" width="19.7109375" style="3" customWidth="1"/>
+    <col min="12546" max="12546" width="21.296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="12547" max="12547" width="14.8984375" style="3" customWidth="1"/>
+    <col min="12548" max="12548" width="16.3984375" style="3" customWidth="1"/>
+    <col min="12549" max="12549" width="19.69921875" style="3" customWidth="1"/>
     <col min="12550" max="12801" width="9" style="3"/>
-    <col min="12802" max="12802" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="12803" max="12803" width="14.85546875" style="3" customWidth="1"/>
-    <col min="12804" max="12804" width="16.42578125" style="3" customWidth="1"/>
-    <col min="12805" max="12805" width="19.7109375" style="3" customWidth="1"/>
+    <col min="12802" max="12802" width="21.296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="12803" max="12803" width="14.8984375" style="3" customWidth="1"/>
+    <col min="12804" max="12804" width="16.3984375" style="3" customWidth="1"/>
+    <col min="12805" max="12805" width="19.69921875" style="3" customWidth="1"/>
     <col min="12806" max="13057" width="9" style="3"/>
-    <col min="13058" max="13058" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="13059" max="13059" width="14.85546875" style="3" customWidth="1"/>
-    <col min="13060" max="13060" width="16.42578125" style="3" customWidth="1"/>
-    <col min="13061" max="13061" width="19.7109375" style="3" customWidth="1"/>
+    <col min="13058" max="13058" width="21.296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="13059" max="13059" width="14.8984375" style="3" customWidth="1"/>
+    <col min="13060" max="13060" width="16.3984375" style="3" customWidth="1"/>
+    <col min="13061" max="13061" width="19.69921875" style="3" customWidth="1"/>
     <col min="13062" max="13313" width="9" style="3"/>
-    <col min="13314" max="13314" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="13315" max="13315" width="14.85546875" style="3" customWidth="1"/>
-    <col min="13316" max="13316" width="16.42578125" style="3" customWidth="1"/>
-    <col min="13317" max="13317" width="19.7109375" style="3" customWidth="1"/>
+    <col min="13314" max="13314" width="21.296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="13315" max="13315" width="14.8984375" style="3" customWidth="1"/>
+    <col min="13316" max="13316" width="16.3984375" style="3" customWidth="1"/>
+    <col min="13317" max="13317" width="19.69921875" style="3" customWidth="1"/>
     <col min="13318" max="13569" width="9" style="3"/>
-    <col min="13570" max="13570" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="13571" max="13571" width="14.85546875" style="3" customWidth="1"/>
-    <col min="13572" max="13572" width="16.42578125" style="3" customWidth="1"/>
-    <col min="13573" max="13573" width="19.7109375" style="3" customWidth="1"/>
+    <col min="13570" max="13570" width="21.296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="13571" max="13571" width="14.8984375" style="3" customWidth="1"/>
+    <col min="13572" max="13572" width="16.3984375" style="3" customWidth="1"/>
+    <col min="13573" max="13573" width="19.69921875" style="3" customWidth="1"/>
     <col min="13574" max="13825" width="9" style="3"/>
-    <col min="13826" max="13826" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="13827" max="13827" width="14.85546875" style="3" customWidth="1"/>
-    <col min="13828" max="13828" width="16.42578125" style="3" customWidth="1"/>
-    <col min="13829" max="13829" width="19.7109375" style="3" customWidth="1"/>
+    <col min="13826" max="13826" width="21.296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="13827" max="13827" width="14.8984375" style="3" customWidth="1"/>
+    <col min="13828" max="13828" width="16.3984375" style="3" customWidth="1"/>
+    <col min="13829" max="13829" width="19.69921875" style="3" customWidth="1"/>
     <col min="13830" max="14081" width="9" style="3"/>
-    <col min="14082" max="14082" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="14083" max="14083" width="14.85546875" style="3" customWidth="1"/>
-    <col min="14084" max="14084" width="16.42578125" style="3" customWidth="1"/>
-    <col min="14085" max="14085" width="19.7109375" style="3" customWidth="1"/>
+    <col min="14082" max="14082" width="21.296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="14083" max="14083" width="14.8984375" style="3" customWidth="1"/>
+    <col min="14084" max="14084" width="16.3984375" style="3" customWidth="1"/>
+    <col min="14085" max="14085" width="19.69921875" style="3" customWidth="1"/>
     <col min="14086" max="14337" width="9" style="3"/>
-    <col min="14338" max="14338" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="14339" max="14339" width="14.85546875" style="3" customWidth="1"/>
-    <col min="14340" max="14340" width="16.42578125" style="3" customWidth="1"/>
-    <col min="14341" max="14341" width="19.7109375" style="3" customWidth="1"/>
+    <col min="14338" max="14338" width="21.296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="14339" max="14339" width="14.8984375" style="3" customWidth="1"/>
+    <col min="14340" max="14340" width="16.3984375" style="3" customWidth="1"/>
+    <col min="14341" max="14341" width="19.69921875" style="3" customWidth="1"/>
     <col min="14342" max="14593" width="9" style="3"/>
-    <col min="14594" max="14594" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="14595" max="14595" width="14.85546875" style="3" customWidth="1"/>
-    <col min="14596" max="14596" width="16.42578125" style="3" customWidth="1"/>
-    <col min="14597" max="14597" width="19.7109375" style="3" customWidth="1"/>
+    <col min="14594" max="14594" width="21.296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="14595" max="14595" width="14.8984375" style="3" customWidth="1"/>
+    <col min="14596" max="14596" width="16.3984375" style="3" customWidth="1"/>
+    <col min="14597" max="14597" width="19.69921875" style="3" customWidth="1"/>
     <col min="14598" max="14849" width="9" style="3"/>
-    <col min="14850" max="14850" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="14851" max="14851" width="14.85546875" style="3" customWidth="1"/>
-    <col min="14852" max="14852" width="16.42578125" style="3" customWidth="1"/>
-    <col min="14853" max="14853" width="19.7109375" style="3" customWidth="1"/>
+    <col min="14850" max="14850" width="21.296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="14851" max="14851" width="14.8984375" style="3" customWidth="1"/>
+    <col min="14852" max="14852" width="16.3984375" style="3" customWidth="1"/>
+    <col min="14853" max="14853" width="19.69921875" style="3" customWidth="1"/>
     <col min="14854" max="15105" width="9" style="3"/>
-    <col min="15106" max="15106" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="15107" max="15107" width="14.85546875" style="3" customWidth="1"/>
-    <col min="15108" max="15108" width="16.42578125" style="3" customWidth="1"/>
-    <col min="15109" max="15109" width="19.7109375" style="3" customWidth="1"/>
+    <col min="15106" max="15106" width="21.296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="15107" max="15107" width="14.8984375" style="3" customWidth="1"/>
+    <col min="15108" max="15108" width="16.3984375" style="3" customWidth="1"/>
+    <col min="15109" max="15109" width="19.69921875" style="3" customWidth="1"/>
     <col min="15110" max="15361" width="9" style="3"/>
-    <col min="15362" max="15362" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="15363" max="15363" width="14.85546875" style="3" customWidth="1"/>
-    <col min="15364" max="15364" width="16.42578125" style="3" customWidth="1"/>
-    <col min="15365" max="15365" width="19.7109375" style="3" customWidth="1"/>
+    <col min="15362" max="15362" width="21.296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="15363" max="15363" width="14.8984375" style="3" customWidth="1"/>
+    <col min="15364" max="15364" width="16.3984375" style="3" customWidth="1"/>
+    <col min="15365" max="15365" width="19.69921875" style="3" customWidth="1"/>
     <col min="15366" max="15617" width="9" style="3"/>
-    <col min="15618" max="15618" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="15619" max="15619" width="14.85546875" style="3" customWidth="1"/>
-    <col min="15620" max="15620" width="16.42578125" style="3" customWidth="1"/>
-    <col min="15621" max="15621" width="19.7109375" style="3" customWidth="1"/>
+    <col min="15618" max="15618" width="21.296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="15619" max="15619" width="14.8984375" style="3" customWidth="1"/>
+    <col min="15620" max="15620" width="16.3984375" style="3" customWidth="1"/>
+    <col min="15621" max="15621" width="19.69921875" style="3" customWidth="1"/>
     <col min="15622" max="15873" width="9" style="3"/>
-    <col min="15874" max="15874" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="15875" max="15875" width="14.85546875" style="3" customWidth="1"/>
-    <col min="15876" max="15876" width="16.42578125" style="3" customWidth="1"/>
-    <col min="15877" max="15877" width="19.7109375" style="3" customWidth="1"/>
+    <col min="15874" max="15874" width="21.296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="15875" max="15875" width="14.8984375" style="3" customWidth="1"/>
+    <col min="15876" max="15876" width="16.3984375" style="3" customWidth="1"/>
+    <col min="15877" max="15877" width="19.69921875" style="3" customWidth="1"/>
     <col min="15878" max="16129" width="9" style="3"/>
-    <col min="16130" max="16130" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="16131" max="16131" width="14.85546875" style="3" customWidth="1"/>
-    <col min="16132" max="16132" width="16.42578125" style="3" customWidth="1"/>
-    <col min="16133" max="16133" width="19.7109375" style="3" customWidth="1"/>
+    <col min="16130" max="16130" width="21.296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="16131" max="16131" width="14.8984375" style="3" customWidth="1"/>
+    <col min="16132" max="16132" width="16.3984375" style="3" customWidth="1"/>
+    <col min="16133" max="16133" width="19.69921875" style="3" customWidth="1"/>
     <col min="16134" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="20.25">
+    <row r="1" spans="1:5" ht="21.6" x14ac:dyDescent="0.4">
       <c r="A1" s="15" t="s">
         <v>14</v>
       </c>
@@ -2391,14 +2418,14 @@
       <c r="D1" s="15"/>
       <c r="E1" s="15"/>
     </row>
-    <row r="2" spans="1:5" ht="20.25">
+    <row r="2" spans="1:5" ht="21.6" x14ac:dyDescent="0.4">
       <c r="A2" s="4"/>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A4" s="5" t="s">
         <v>15</v>
       </c>
@@ -2415,7 +2442,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A5" s="6">
         <v>1</v>
       </c>
@@ -2424,7 +2451,7 @@
       <c r="D5" s="6"/>
       <c r="E5" s="6"/>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A6" s="6">
         <v>2</v>
       </c>
@@ -2433,7 +2460,7 @@
       <c r="D6" s="6"/>
       <c r="E6" s="6"/>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A7" s="6">
         <v>3</v>
       </c>
@@ -2442,175 +2469,175 @@
       <c r="D7" s="6"/>
       <c r="E7" s="6"/>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A8" s="6"/>
       <c r="B8" s="6"/>
       <c r="C8" s="6"/>
       <c r="D8" s="6"/>
       <c r="E8" s="6"/>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A9" s="6"/>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
       <c r="D9" s="6"/>
       <c r="E9" s="6"/>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A10" s="6"/>
       <c r="B10" s="6"/>
       <c r="C10" s="6"/>
       <c r="D10" s="6"/>
       <c r="E10" s="6"/>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A11" s="6"/>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
       <c r="D11" s="6"/>
       <c r="E11" s="6"/>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A12" s="6"/>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
       <c r="D12" s="6"/>
       <c r="E12" s="6"/>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A13" s="6"/>
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
       <c r="E13" s="6"/>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A14" s="6"/>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
       <c r="D14" s="6"/>
       <c r="E14" s="6"/>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A15" s="6"/>
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
       <c r="E15" s="6"/>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A16" s="6"/>
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
       <c r="D16" s="6"/>
       <c r="E16" s="6"/>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A17" s="6"/>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
       <c r="D17" s="6"/>
       <c r="E17" s="6"/>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A18" s="6"/>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
       <c r="D18" s="6"/>
       <c r="E18" s="6"/>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A19" s="6"/>
       <c r="B19" s="6"/>
       <c r="C19" s="6"/>
       <c r="D19" s="6"/>
       <c r="E19" s="6"/>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A20" s="6"/>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
       <c r="D20" s="6"/>
       <c r="E20" s="6"/>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A21" s="6"/>
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
       <c r="D21" s="6"/>
       <c r="E21" s="6"/>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A22" s="6"/>
       <c r="B22" s="6"/>
       <c r="C22" s="6"/>
       <c r="D22" s="6"/>
       <c r="E22" s="6"/>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A23" s="6"/>
       <c r="B23" s="6"/>
       <c r="C23" s="6"/>
       <c r="D23" s="6"/>
       <c r="E23" s="6"/>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A24" s="6"/>
       <c r="B24" s="6"/>
       <c r="C24" s="6"/>
       <c r="D24" s="6"/>
       <c r="E24" s="6"/>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A25" s="6"/>
       <c r="B25" s="6"/>
       <c r="C25" s="6"/>
       <c r="D25" s="6"/>
       <c r="E25" s="6"/>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A26" s="6"/>
       <c r="B26" s="6"/>
       <c r="C26" s="6"/>
       <c r="D26" s="6"/>
       <c r="E26" s="6"/>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A27" s="6"/>
       <c r="B27" s="6"/>
       <c r="C27" s="6"/>
       <c r="D27" s="6"/>
       <c r="E27" s="6"/>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A28" s="6"/>
       <c r="B28" s="6"/>
       <c r="C28" s="6"/>
       <c r="D28" s="6"/>
       <c r="E28" s="6"/>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A29" s="6"/>
       <c r="B29" s="6"/>
       <c r="C29" s="6"/>
       <c r="D29" s="6"/>
       <c r="E29" s="6"/>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A30" s="6"/>
       <c r="B30" s="6"/>
       <c r="C30" s="6"/>
       <c r="D30" s="6"/>
       <c r="E30" s="6"/>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A31" s="6"/>
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
       <c r="D31" s="6"/>
       <c r="E31" s="6"/>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A32" s="6"/>
       <c r="B32" s="6"/>
       <c r="C32" s="6"/>
@@ -2623,7 +2650,7 @@
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <dataValidations xWindow="335" yWindow="435" count="1">
-    <dataValidation type="textLength" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="부서ID는 회사ID 및 개인ID와 중복되지 않은 것으로서 _x000a_3~9자리의 영문,숫자의 조합으로 만듭니다._x000a_" sqref="C1:C1048576">
+    <dataValidation type="textLength" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="부서ID는 회사ID 및 개인ID와 중복되지 않은 것으로서 _x000a_3~9자리의 영문,숫자의 조합으로 만듭니다._x000a_" sqref="C1:C1048576" xr:uid="{00000000-0002-0000-0300-000000000000}">
       <formula1>3</formula1>
       <formula2>9</formula2>
     </dataValidation>

--- a/docs/tech/조직도 등록메뉴얼.xlsx
+++ b/docs/tech/조직도 등록메뉴얼.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="21727"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\JAVA\OPENSOLUTION\BASIC\EzFlowMasterOnlyPull\ezFlow4Java\docs\tech\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Projects\kaoni\jmocha\ezFlow4Java\docs\tech\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05101BA5-85C4-411B-9FE9-05B5F01215B2}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="15" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="15" windowWidth="29040" windowHeight="16440"/>
   </bookViews>
   <sheets>
     <sheet name="작성시유의사항" sheetId="2" r:id="rId1"/>
@@ -18,7 +17,7 @@
     <sheet name="예시" sheetId="4" state="hidden" r:id="rId3"/>
     <sheet name="부서정보" sheetId="3" state="hidden" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -262,14 +261,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>④ 생년월일 입력시 주민등록번호 앞 6자리만 입력한다. (또는 0000-00-00)</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>⑤ 이동전화 입력시 전화번호11자리만 입력한다. (또는 000-0000-0000)</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>⑥ 모든 셀에 공백이 있어서는 안된다.</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -323,21 +314,27 @@
   <si>
     <t>사번</t>
     <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>④ 생년월일 입력시 0000-00-00 형식으로 입력</t>
+  </si>
+  <si>
+    <t>⑤ 이동전화 입력시 000-0000-0000 형식으로 입력</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="2">
-    <numFmt numFmtId="176" formatCode="000\-0000\-0000"/>
-    <numFmt numFmtId="177" formatCode="\1\900\-00\-00"/>
+    <numFmt numFmtId="164" formatCode="000\-0000\-0000"/>
+    <numFmt numFmtId="165" formatCode="\1\900\-00\-00"/>
   </numFmts>
-  <fonts count="26" x14ac:knownFonts="1">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -345,7 +342,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -353,7 +350,7 @@
     <font>
       <sz val="18"/>
       <color theme="3"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri Light"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="major"/>
@@ -362,7 +359,7 @@
       <b/>
       <sz val="15"/>
       <color theme="3"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -371,7 +368,7 @@
       <b/>
       <sz val="13"/>
       <color theme="3"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -380,7 +377,7 @@
       <b/>
       <sz val="11"/>
       <color theme="3"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -388,7 +385,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -396,7 +393,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -404,7 +401,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -412,7 +409,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -421,7 +418,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -430,7 +427,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -438,7 +435,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -447,7 +444,7 @@
       <b/>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -455,7 +452,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -464,7 +461,7 @@
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -473,7 +470,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -481,14 +478,14 @@
     <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -496,7 +493,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -533,7 +530,7 @@
     <font>
       <sz val="15"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -541,7 +538,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -1003,10 +1000,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
@@ -1122,7 +1119,7 @@
         <xdr:cNvPr id="2" name="그림 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1182,7 +1179,7 @@
         <xdr:cNvPr id="3" name="그림 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1479,19 +1476,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B3:S42"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.296875" style="10" customWidth="1"/>
-    <col min="2" max="2" width="12.296875" style="10" customWidth="1"/>
-    <col min="3" max="3" width="11.09765625" style="10" customWidth="1"/>
+    <col min="1" max="1" width="4.28515625" style="10" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="10" customWidth="1"/>
+    <col min="3" max="3" width="11.140625" style="10" customWidth="1"/>
     <col min="4" max="8" width="9" style="10"/>
-    <col min="9" max="9" width="11.8984375" style="10" customWidth="1"/>
+    <col min="9" max="9" width="11.85546875" style="10" customWidth="1"/>
     <col min="10" max="16384" width="9" style="10"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:11" s="8" customFormat="1" ht="24" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:11" s="8" customFormat="1" ht="24">
       <c r="B3" s="7" t="s">
         <v>58</v>
       </c>
@@ -1500,97 +1497,97 @@
       </c>
       <c r="K3" s="7"/>
     </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:11">
       <c r="B4" s="9"/>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:11">
       <c r="B5" s="9" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J5" s="10" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.4">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11">
       <c r="B6" s="11" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="J6" s="10" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:11">
       <c r="B7" s="11" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="J7" s="10" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:11">
       <c r="B8" s="11" t="s">
         <v>59</v>
       </c>
       <c r="J8" s="10" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.4">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="9" spans="2:11">
       <c r="B9" s="11" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="J9" s="10" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.4">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="10" spans="2:11">
       <c r="B10" s="11" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="J10" s="10" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.4">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="11" spans="2:11">
       <c r="B11" s="11" t="s">
         <v>60</v>
       </c>
       <c r="J11" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="12" spans="2:11">
+      <c r="J12" s="10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="13" spans="2:11">
+      <c r="B13" s="11"/>
+    </row>
+    <row r="14" spans="2:11">
+      <c r="B14" s="11"/>
+    </row>
+    <row r="15" spans="2:11">
+      <c r="B15" s="11"/>
+    </row>
+    <row r="18" spans="2:19" ht="24">
+      <c r="S18" s="7"/>
+    </row>
+    <row r="32" spans="2:19">
+      <c r="B32" s="12"/>
+    </row>
+    <row r="35" spans="2:3" hidden="1">
+      <c r="B35" s="14" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="J12" s="10" t="s">
+    <row r="36" spans="2:3" hidden="1">
+      <c r="B36" s="14" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B13" s="11"/>
-    </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B14" s="11"/>
-    </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B15" s="11"/>
-    </row>
-    <row r="18" spans="2:19" ht="24" x14ac:dyDescent="0.4">
-      <c r="S18" s="7"/>
-    </row>
-    <row r="32" spans="2:19" x14ac:dyDescent="0.4">
-      <c r="B32" s="12"/>
-    </row>
-    <row r="35" spans="2:3" hidden="1" x14ac:dyDescent="0.4">
-      <c r="B35" s="14" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="36" spans="2:3" hidden="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="14" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="37" spans="2:3" hidden="1" x14ac:dyDescent="0.4"/>
-    <row r="42" spans="2:3" x14ac:dyDescent="0.4">
+    <row r="37" spans="2:3" hidden="1"/>
+    <row r="42" spans="2:3">
       <c r="B42" s="13"/>
       <c r="C42" s="13"/>
     </row>
@@ -1603,23 +1600,23 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Q2"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="13" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.09765625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.09765625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.3984375" customWidth="1"/>
-    <col min="14" max="14" width="11.09765625" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.3984375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.3984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.42578125" customWidth="1"/>
+    <col min="14" max="14" width="11.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:17">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1651,13 +1648,13 @@
         <v>9</v>
       </c>
       <c r="K1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="L1" t="s">
         <v>20</v>
       </c>
       <c r="M1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="N1" s="2" t="s">
         <v>10</v>
@@ -1672,7 +1669,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:17">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1684,15 +1681,15 @@
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <dataValidations count="3">
-    <dataValidation type="textLength" showInputMessage="1" showErrorMessage="1" prompt="회사ID 및 부서ID와 중복되지 않은 유일한것으로서 _x000a_3~9자리의 영문,숫자의 조합으로 만듭니다._x000a_" sqref="I1:I1048576" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="textLength" showInputMessage="1" showErrorMessage="1" prompt="회사ID 및 부서ID와 중복되지 않은 유일한것으로서 _x000a_3~9자리의 영문,숫자의 조합으로 만듭니다._x000a_" sqref="I1:I1048576">
       <formula1>3</formula1>
       <formula2>9</formula2>
     </dataValidation>
-    <dataValidation type="textLength" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E10 D1:D288 F1:F372" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="textLength" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E10 D1:D288 F1:F372">
       <formula1>3</formula1>
       <formula2>9</formula2>
     </dataValidation>
-    <dataValidation type="textLength" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="8~12자리의영문,숫자,특수문자의 조합으로 생성합니다." sqref="L1:L1048576" xr:uid="{00000000-0002-0000-0100-000002000000}">
+    <dataValidation type="textLength" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="8~12자리의영문,숫자,특수문자의 조합으로 생성합니다." sqref="L1:L1048576">
       <formula1>8</formula1>
       <formula2>12</formula2>
     </dataValidation>
@@ -1702,7 +1699,7 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000003000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>작성시유의사항!$B$35:$B$36</xm:f>
           </x14:formula1>
@@ -1715,23 +1712,23 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:O10"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="13" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.09765625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.09765625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.3984375" customWidth="1"/>
-    <col min="12" max="12" width="11.09765625" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.3984375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.3984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.42578125" customWidth="1"/>
+    <col min="12" max="12" width="11.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1778,7 +1775,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:15">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1799,7 +1796,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:15">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1820,7 +1817,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:15">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1841,7 +1838,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:15">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1862,7 +1859,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:15">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1883,7 +1880,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:15">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1922,7 +1919,7 @@
         <v>1056235623</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:15">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1943,7 +1940,7 @@
         <v>49</v>
       </c>
       <c r="I8" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="J8" t="s">
         <v>50</v>
@@ -1961,7 +1958,7 @@
         <v>1089568956</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:15">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2000,7 +1997,7 @@
         <v>1045124512</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:15">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2042,18 +2039,18 @@
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <dataValidations xWindow="788" yWindow="443" count="4">
-    <dataValidation type="textLength" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E10 F1:F10 F12 D1:D10 D12" xr:uid="{00000000-0002-0000-0200-000000000000}">
+    <dataValidation type="textLength" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E10 F1:F10 F12 D1:D10 D12">
       <formula1>3</formula1>
       <formula2>9</formula2>
     </dataValidation>
-    <dataValidation type="textLength" showInputMessage="1" showErrorMessage="1" prompt="회사ID 및 부서ID와 중복되지 않은 유일한것으로서 _x000a_3~9자리의 영문,숫자의 조합으로 만듭니다._x000a_" sqref="I1:I10 I12:I1048576" xr:uid="{00000000-0002-0000-0200-000001000000}">
+    <dataValidation type="textLength" showInputMessage="1" showErrorMessage="1" prompt="회사ID 및 부서ID와 중복되지 않은 유일한것으로서 _x000a_3~9자리의 영문,숫자의 조합으로 만듭니다._x000a_" sqref="I1:I10 I12:I1048576">
       <formula1>3</formula1>
       <formula2>9</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M12" xr:uid="{00000000-0002-0000-0200-000002000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M12">
       <formula1>$U$32:$U$33</formula1>
     </dataValidation>
-    <dataValidation type="textLength" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="8~12자리의영문,숫자,특수문자의 조합으로 생성합니다." sqref="K1:K1048576" xr:uid="{00000000-0002-0000-0200-000003000000}">
+    <dataValidation type="textLength" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="8~12자리의영문,숫자,특수문자의 조합으로 생성합니다." sqref="K1:K1048576">
       <formula1>8</formula1>
       <formula2>12</formula2>
     </dataValidation>
@@ -2063,13 +2060,13 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xWindow="788" yWindow="443" count="2">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0200-000004000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>작성시유의사항!$U$32:$U$33</xm:f>
           </x14:formula1>
           <xm:sqref>M2:M10</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0200-000005000000}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>작성시유의사항!$B$35:$B$36</xm:f>
           </x14:formula1>
@@ -2082,334 +2079,334 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E32"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
-    <col min="2" max="2" width="21.296875" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.8984375" style="3" customWidth="1"/>
-    <col min="4" max="4" width="16.3984375" style="3" customWidth="1"/>
-    <col min="5" max="5" width="19.69921875" style="3" customWidth="1"/>
+    <col min="2" max="2" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.85546875" style="3" customWidth="1"/>
+    <col min="4" max="4" width="16.42578125" style="3" customWidth="1"/>
+    <col min="5" max="5" width="19.7109375" style="3" customWidth="1"/>
     <col min="6" max="257" width="9" style="3"/>
-    <col min="258" max="258" width="21.296875" style="3" bestFit="1" customWidth="1"/>
-    <col min="259" max="259" width="14.8984375" style="3" customWidth="1"/>
-    <col min="260" max="260" width="16.3984375" style="3" customWidth="1"/>
-    <col min="261" max="261" width="19.69921875" style="3" customWidth="1"/>
+    <col min="258" max="258" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="259" max="259" width="14.85546875" style="3" customWidth="1"/>
+    <col min="260" max="260" width="16.42578125" style="3" customWidth="1"/>
+    <col min="261" max="261" width="19.7109375" style="3" customWidth="1"/>
     <col min="262" max="513" width="9" style="3"/>
-    <col min="514" max="514" width="21.296875" style="3" bestFit="1" customWidth="1"/>
-    <col min="515" max="515" width="14.8984375" style="3" customWidth="1"/>
-    <col min="516" max="516" width="16.3984375" style="3" customWidth="1"/>
-    <col min="517" max="517" width="19.69921875" style="3" customWidth="1"/>
+    <col min="514" max="514" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="515" max="515" width="14.85546875" style="3" customWidth="1"/>
+    <col min="516" max="516" width="16.42578125" style="3" customWidth="1"/>
+    <col min="517" max="517" width="19.7109375" style="3" customWidth="1"/>
     <col min="518" max="769" width="9" style="3"/>
-    <col min="770" max="770" width="21.296875" style="3" bestFit="1" customWidth="1"/>
-    <col min="771" max="771" width="14.8984375" style="3" customWidth="1"/>
-    <col min="772" max="772" width="16.3984375" style="3" customWidth="1"/>
-    <col min="773" max="773" width="19.69921875" style="3" customWidth="1"/>
+    <col min="770" max="770" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="771" max="771" width="14.85546875" style="3" customWidth="1"/>
+    <col min="772" max="772" width="16.42578125" style="3" customWidth="1"/>
+    <col min="773" max="773" width="19.7109375" style="3" customWidth="1"/>
     <col min="774" max="1025" width="9" style="3"/>
-    <col min="1026" max="1026" width="21.296875" style="3" bestFit="1" customWidth="1"/>
-    <col min="1027" max="1027" width="14.8984375" style="3" customWidth="1"/>
-    <col min="1028" max="1028" width="16.3984375" style="3" customWidth="1"/>
-    <col min="1029" max="1029" width="19.69921875" style="3" customWidth="1"/>
+    <col min="1026" max="1026" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="1027" max="1027" width="14.85546875" style="3" customWidth="1"/>
+    <col min="1028" max="1028" width="16.42578125" style="3" customWidth="1"/>
+    <col min="1029" max="1029" width="19.7109375" style="3" customWidth="1"/>
     <col min="1030" max="1281" width="9" style="3"/>
-    <col min="1282" max="1282" width="21.296875" style="3" bestFit="1" customWidth="1"/>
-    <col min="1283" max="1283" width="14.8984375" style="3" customWidth="1"/>
-    <col min="1284" max="1284" width="16.3984375" style="3" customWidth="1"/>
-    <col min="1285" max="1285" width="19.69921875" style="3" customWidth="1"/>
+    <col min="1282" max="1282" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="1283" max="1283" width="14.85546875" style="3" customWidth="1"/>
+    <col min="1284" max="1284" width="16.42578125" style="3" customWidth="1"/>
+    <col min="1285" max="1285" width="19.7109375" style="3" customWidth="1"/>
     <col min="1286" max="1537" width="9" style="3"/>
-    <col min="1538" max="1538" width="21.296875" style="3" bestFit="1" customWidth="1"/>
-    <col min="1539" max="1539" width="14.8984375" style="3" customWidth="1"/>
-    <col min="1540" max="1540" width="16.3984375" style="3" customWidth="1"/>
-    <col min="1541" max="1541" width="19.69921875" style="3" customWidth="1"/>
+    <col min="1538" max="1538" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="1539" max="1539" width="14.85546875" style="3" customWidth="1"/>
+    <col min="1540" max="1540" width="16.42578125" style="3" customWidth="1"/>
+    <col min="1541" max="1541" width="19.7109375" style="3" customWidth="1"/>
     <col min="1542" max="1793" width="9" style="3"/>
-    <col min="1794" max="1794" width="21.296875" style="3" bestFit="1" customWidth="1"/>
-    <col min="1795" max="1795" width="14.8984375" style="3" customWidth="1"/>
-    <col min="1796" max="1796" width="16.3984375" style="3" customWidth="1"/>
-    <col min="1797" max="1797" width="19.69921875" style="3" customWidth="1"/>
+    <col min="1794" max="1794" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="1795" max="1795" width="14.85546875" style="3" customWidth="1"/>
+    <col min="1796" max="1796" width="16.42578125" style="3" customWidth="1"/>
+    <col min="1797" max="1797" width="19.7109375" style="3" customWidth="1"/>
     <col min="1798" max="2049" width="9" style="3"/>
-    <col min="2050" max="2050" width="21.296875" style="3" bestFit="1" customWidth="1"/>
-    <col min="2051" max="2051" width="14.8984375" style="3" customWidth="1"/>
-    <col min="2052" max="2052" width="16.3984375" style="3" customWidth="1"/>
-    <col min="2053" max="2053" width="19.69921875" style="3" customWidth="1"/>
+    <col min="2050" max="2050" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="2051" max="2051" width="14.85546875" style="3" customWidth="1"/>
+    <col min="2052" max="2052" width="16.42578125" style="3" customWidth="1"/>
+    <col min="2053" max="2053" width="19.7109375" style="3" customWidth="1"/>
     <col min="2054" max="2305" width="9" style="3"/>
-    <col min="2306" max="2306" width="21.296875" style="3" bestFit="1" customWidth="1"/>
-    <col min="2307" max="2307" width="14.8984375" style="3" customWidth="1"/>
-    <col min="2308" max="2308" width="16.3984375" style="3" customWidth="1"/>
-    <col min="2309" max="2309" width="19.69921875" style="3" customWidth="1"/>
+    <col min="2306" max="2306" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="2307" max="2307" width="14.85546875" style="3" customWidth="1"/>
+    <col min="2308" max="2308" width="16.42578125" style="3" customWidth="1"/>
+    <col min="2309" max="2309" width="19.7109375" style="3" customWidth="1"/>
     <col min="2310" max="2561" width="9" style="3"/>
-    <col min="2562" max="2562" width="21.296875" style="3" bestFit="1" customWidth="1"/>
-    <col min="2563" max="2563" width="14.8984375" style="3" customWidth="1"/>
-    <col min="2564" max="2564" width="16.3984375" style="3" customWidth="1"/>
-    <col min="2565" max="2565" width="19.69921875" style="3" customWidth="1"/>
+    <col min="2562" max="2562" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="2563" max="2563" width="14.85546875" style="3" customWidth="1"/>
+    <col min="2564" max="2564" width="16.42578125" style="3" customWidth="1"/>
+    <col min="2565" max="2565" width="19.7109375" style="3" customWidth="1"/>
     <col min="2566" max="2817" width="9" style="3"/>
-    <col min="2818" max="2818" width="21.296875" style="3" bestFit="1" customWidth="1"/>
-    <col min="2819" max="2819" width="14.8984375" style="3" customWidth="1"/>
-    <col min="2820" max="2820" width="16.3984375" style="3" customWidth="1"/>
-    <col min="2821" max="2821" width="19.69921875" style="3" customWidth="1"/>
+    <col min="2818" max="2818" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="2819" max="2819" width="14.85546875" style="3" customWidth="1"/>
+    <col min="2820" max="2820" width="16.42578125" style="3" customWidth="1"/>
+    <col min="2821" max="2821" width="19.7109375" style="3" customWidth="1"/>
     <col min="2822" max="3073" width="9" style="3"/>
-    <col min="3074" max="3074" width="21.296875" style="3" bestFit="1" customWidth="1"/>
-    <col min="3075" max="3075" width="14.8984375" style="3" customWidth="1"/>
-    <col min="3076" max="3076" width="16.3984375" style="3" customWidth="1"/>
-    <col min="3077" max="3077" width="19.69921875" style="3" customWidth="1"/>
+    <col min="3074" max="3074" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3075" max="3075" width="14.85546875" style="3" customWidth="1"/>
+    <col min="3076" max="3076" width="16.42578125" style="3" customWidth="1"/>
+    <col min="3077" max="3077" width="19.7109375" style="3" customWidth="1"/>
     <col min="3078" max="3329" width="9" style="3"/>
-    <col min="3330" max="3330" width="21.296875" style="3" bestFit="1" customWidth="1"/>
-    <col min="3331" max="3331" width="14.8984375" style="3" customWidth="1"/>
-    <col min="3332" max="3332" width="16.3984375" style="3" customWidth="1"/>
-    <col min="3333" max="3333" width="19.69921875" style="3" customWidth="1"/>
+    <col min="3330" max="3330" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3331" max="3331" width="14.85546875" style="3" customWidth="1"/>
+    <col min="3332" max="3332" width="16.42578125" style="3" customWidth="1"/>
+    <col min="3333" max="3333" width="19.7109375" style="3" customWidth="1"/>
     <col min="3334" max="3585" width="9" style="3"/>
-    <col min="3586" max="3586" width="21.296875" style="3" bestFit="1" customWidth="1"/>
-    <col min="3587" max="3587" width="14.8984375" style="3" customWidth="1"/>
-    <col min="3588" max="3588" width="16.3984375" style="3" customWidth="1"/>
-    <col min="3589" max="3589" width="19.69921875" style="3" customWidth="1"/>
+    <col min="3586" max="3586" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3587" max="3587" width="14.85546875" style="3" customWidth="1"/>
+    <col min="3588" max="3588" width="16.42578125" style="3" customWidth="1"/>
+    <col min="3589" max="3589" width="19.7109375" style="3" customWidth="1"/>
     <col min="3590" max="3841" width="9" style="3"/>
-    <col min="3842" max="3842" width="21.296875" style="3" bestFit="1" customWidth="1"/>
-    <col min="3843" max="3843" width="14.8984375" style="3" customWidth="1"/>
-    <col min="3844" max="3844" width="16.3984375" style="3" customWidth="1"/>
-    <col min="3845" max="3845" width="19.69921875" style="3" customWidth="1"/>
+    <col min="3842" max="3842" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3843" max="3843" width="14.85546875" style="3" customWidth="1"/>
+    <col min="3844" max="3844" width="16.42578125" style="3" customWidth="1"/>
+    <col min="3845" max="3845" width="19.7109375" style="3" customWidth="1"/>
     <col min="3846" max="4097" width="9" style="3"/>
-    <col min="4098" max="4098" width="21.296875" style="3" bestFit="1" customWidth="1"/>
-    <col min="4099" max="4099" width="14.8984375" style="3" customWidth="1"/>
-    <col min="4100" max="4100" width="16.3984375" style="3" customWidth="1"/>
-    <col min="4101" max="4101" width="19.69921875" style="3" customWidth="1"/>
+    <col min="4098" max="4098" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="4099" max="4099" width="14.85546875" style="3" customWidth="1"/>
+    <col min="4100" max="4100" width="16.42578125" style="3" customWidth="1"/>
+    <col min="4101" max="4101" width="19.7109375" style="3" customWidth="1"/>
     <col min="4102" max="4353" width="9" style="3"/>
-    <col min="4354" max="4354" width="21.296875" style="3" bestFit="1" customWidth="1"/>
-    <col min="4355" max="4355" width="14.8984375" style="3" customWidth="1"/>
-    <col min="4356" max="4356" width="16.3984375" style="3" customWidth="1"/>
-    <col min="4357" max="4357" width="19.69921875" style="3" customWidth="1"/>
+    <col min="4354" max="4354" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="4355" max="4355" width="14.85546875" style="3" customWidth="1"/>
+    <col min="4356" max="4356" width="16.42578125" style="3" customWidth="1"/>
+    <col min="4357" max="4357" width="19.7109375" style="3" customWidth="1"/>
     <col min="4358" max="4609" width="9" style="3"/>
-    <col min="4610" max="4610" width="21.296875" style="3" bestFit="1" customWidth="1"/>
-    <col min="4611" max="4611" width="14.8984375" style="3" customWidth="1"/>
-    <col min="4612" max="4612" width="16.3984375" style="3" customWidth="1"/>
-    <col min="4613" max="4613" width="19.69921875" style="3" customWidth="1"/>
+    <col min="4610" max="4610" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="4611" max="4611" width="14.85546875" style="3" customWidth="1"/>
+    <col min="4612" max="4612" width="16.42578125" style="3" customWidth="1"/>
+    <col min="4613" max="4613" width="19.7109375" style="3" customWidth="1"/>
     <col min="4614" max="4865" width="9" style="3"/>
-    <col min="4866" max="4866" width="21.296875" style="3" bestFit="1" customWidth="1"/>
-    <col min="4867" max="4867" width="14.8984375" style="3" customWidth="1"/>
-    <col min="4868" max="4868" width="16.3984375" style="3" customWidth="1"/>
-    <col min="4869" max="4869" width="19.69921875" style="3" customWidth="1"/>
+    <col min="4866" max="4866" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="4867" max="4867" width="14.85546875" style="3" customWidth="1"/>
+    <col min="4868" max="4868" width="16.42578125" style="3" customWidth="1"/>
+    <col min="4869" max="4869" width="19.7109375" style="3" customWidth="1"/>
     <col min="4870" max="5121" width="9" style="3"/>
-    <col min="5122" max="5122" width="21.296875" style="3" bestFit="1" customWidth="1"/>
-    <col min="5123" max="5123" width="14.8984375" style="3" customWidth="1"/>
-    <col min="5124" max="5124" width="16.3984375" style="3" customWidth="1"/>
-    <col min="5125" max="5125" width="19.69921875" style="3" customWidth="1"/>
+    <col min="5122" max="5122" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="5123" max="5123" width="14.85546875" style="3" customWidth="1"/>
+    <col min="5124" max="5124" width="16.42578125" style="3" customWidth="1"/>
+    <col min="5125" max="5125" width="19.7109375" style="3" customWidth="1"/>
     <col min="5126" max="5377" width="9" style="3"/>
-    <col min="5378" max="5378" width="21.296875" style="3" bestFit="1" customWidth="1"/>
-    <col min="5379" max="5379" width="14.8984375" style="3" customWidth="1"/>
-    <col min="5380" max="5380" width="16.3984375" style="3" customWidth="1"/>
-    <col min="5381" max="5381" width="19.69921875" style="3" customWidth="1"/>
+    <col min="5378" max="5378" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="5379" max="5379" width="14.85546875" style="3" customWidth="1"/>
+    <col min="5380" max="5380" width="16.42578125" style="3" customWidth="1"/>
+    <col min="5381" max="5381" width="19.7109375" style="3" customWidth="1"/>
     <col min="5382" max="5633" width="9" style="3"/>
-    <col min="5634" max="5634" width="21.296875" style="3" bestFit="1" customWidth="1"/>
-    <col min="5635" max="5635" width="14.8984375" style="3" customWidth="1"/>
-    <col min="5636" max="5636" width="16.3984375" style="3" customWidth="1"/>
-    <col min="5637" max="5637" width="19.69921875" style="3" customWidth="1"/>
+    <col min="5634" max="5634" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="5635" max="5635" width="14.85546875" style="3" customWidth="1"/>
+    <col min="5636" max="5636" width="16.42578125" style="3" customWidth="1"/>
+    <col min="5637" max="5637" width="19.7109375" style="3" customWidth="1"/>
     <col min="5638" max="5889" width="9" style="3"/>
-    <col min="5890" max="5890" width="21.296875" style="3" bestFit="1" customWidth="1"/>
-    <col min="5891" max="5891" width="14.8984375" style="3" customWidth="1"/>
-    <col min="5892" max="5892" width="16.3984375" style="3" customWidth="1"/>
-    <col min="5893" max="5893" width="19.69921875" style="3" customWidth="1"/>
+    <col min="5890" max="5890" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="5891" max="5891" width="14.85546875" style="3" customWidth="1"/>
+    <col min="5892" max="5892" width="16.42578125" style="3" customWidth="1"/>
+    <col min="5893" max="5893" width="19.7109375" style="3" customWidth="1"/>
     <col min="5894" max="6145" width="9" style="3"/>
-    <col min="6146" max="6146" width="21.296875" style="3" bestFit="1" customWidth="1"/>
-    <col min="6147" max="6147" width="14.8984375" style="3" customWidth="1"/>
-    <col min="6148" max="6148" width="16.3984375" style="3" customWidth="1"/>
-    <col min="6149" max="6149" width="19.69921875" style="3" customWidth="1"/>
+    <col min="6146" max="6146" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="6147" max="6147" width="14.85546875" style="3" customWidth="1"/>
+    <col min="6148" max="6148" width="16.42578125" style="3" customWidth="1"/>
+    <col min="6149" max="6149" width="19.7109375" style="3" customWidth="1"/>
     <col min="6150" max="6401" width="9" style="3"/>
-    <col min="6402" max="6402" width="21.296875" style="3" bestFit="1" customWidth="1"/>
-    <col min="6403" max="6403" width="14.8984375" style="3" customWidth="1"/>
-    <col min="6404" max="6404" width="16.3984375" style="3" customWidth="1"/>
-    <col min="6405" max="6405" width="19.69921875" style="3" customWidth="1"/>
+    <col min="6402" max="6402" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="6403" max="6403" width="14.85546875" style="3" customWidth="1"/>
+    <col min="6404" max="6404" width="16.42578125" style="3" customWidth="1"/>
+    <col min="6405" max="6405" width="19.7109375" style="3" customWidth="1"/>
     <col min="6406" max="6657" width="9" style="3"/>
-    <col min="6658" max="6658" width="21.296875" style="3" bestFit="1" customWidth="1"/>
-    <col min="6659" max="6659" width="14.8984375" style="3" customWidth="1"/>
-    <col min="6660" max="6660" width="16.3984375" style="3" customWidth="1"/>
-    <col min="6661" max="6661" width="19.69921875" style="3" customWidth="1"/>
+    <col min="6658" max="6658" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="6659" max="6659" width="14.85546875" style="3" customWidth="1"/>
+    <col min="6660" max="6660" width="16.42578125" style="3" customWidth="1"/>
+    <col min="6661" max="6661" width="19.7109375" style="3" customWidth="1"/>
     <col min="6662" max="6913" width="9" style="3"/>
-    <col min="6914" max="6914" width="21.296875" style="3" bestFit="1" customWidth="1"/>
-    <col min="6915" max="6915" width="14.8984375" style="3" customWidth="1"/>
-    <col min="6916" max="6916" width="16.3984375" style="3" customWidth="1"/>
-    <col min="6917" max="6917" width="19.69921875" style="3" customWidth="1"/>
+    <col min="6914" max="6914" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="6915" max="6915" width="14.85546875" style="3" customWidth="1"/>
+    <col min="6916" max="6916" width="16.42578125" style="3" customWidth="1"/>
+    <col min="6917" max="6917" width="19.7109375" style="3" customWidth="1"/>
     <col min="6918" max="7169" width="9" style="3"/>
-    <col min="7170" max="7170" width="21.296875" style="3" bestFit="1" customWidth="1"/>
-    <col min="7171" max="7171" width="14.8984375" style="3" customWidth="1"/>
-    <col min="7172" max="7172" width="16.3984375" style="3" customWidth="1"/>
-    <col min="7173" max="7173" width="19.69921875" style="3" customWidth="1"/>
+    <col min="7170" max="7170" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="7171" max="7171" width="14.85546875" style="3" customWidth="1"/>
+    <col min="7172" max="7172" width="16.42578125" style="3" customWidth="1"/>
+    <col min="7173" max="7173" width="19.7109375" style="3" customWidth="1"/>
     <col min="7174" max="7425" width="9" style="3"/>
-    <col min="7426" max="7426" width="21.296875" style="3" bestFit="1" customWidth="1"/>
-    <col min="7427" max="7427" width="14.8984375" style="3" customWidth="1"/>
-    <col min="7428" max="7428" width="16.3984375" style="3" customWidth="1"/>
-    <col min="7429" max="7429" width="19.69921875" style="3" customWidth="1"/>
+    <col min="7426" max="7426" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="7427" max="7427" width="14.85546875" style="3" customWidth="1"/>
+    <col min="7428" max="7428" width="16.42578125" style="3" customWidth="1"/>
+    <col min="7429" max="7429" width="19.7109375" style="3" customWidth="1"/>
     <col min="7430" max="7681" width="9" style="3"/>
-    <col min="7682" max="7682" width="21.296875" style="3" bestFit="1" customWidth="1"/>
-    <col min="7683" max="7683" width="14.8984375" style="3" customWidth="1"/>
-    <col min="7684" max="7684" width="16.3984375" style="3" customWidth="1"/>
-    <col min="7685" max="7685" width="19.69921875" style="3" customWidth="1"/>
+    <col min="7682" max="7682" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="7683" max="7683" width="14.85546875" style="3" customWidth="1"/>
+    <col min="7684" max="7684" width="16.42578125" style="3" customWidth="1"/>
+    <col min="7685" max="7685" width="19.7109375" style="3" customWidth="1"/>
     <col min="7686" max="7937" width="9" style="3"/>
-    <col min="7938" max="7938" width="21.296875" style="3" bestFit="1" customWidth="1"/>
-    <col min="7939" max="7939" width="14.8984375" style="3" customWidth="1"/>
-    <col min="7940" max="7940" width="16.3984375" style="3" customWidth="1"/>
-    <col min="7941" max="7941" width="19.69921875" style="3" customWidth="1"/>
+    <col min="7938" max="7938" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="7939" max="7939" width="14.85546875" style="3" customWidth="1"/>
+    <col min="7940" max="7940" width="16.42578125" style="3" customWidth="1"/>
+    <col min="7941" max="7941" width="19.7109375" style="3" customWidth="1"/>
     <col min="7942" max="8193" width="9" style="3"/>
-    <col min="8194" max="8194" width="21.296875" style="3" bestFit="1" customWidth="1"/>
-    <col min="8195" max="8195" width="14.8984375" style="3" customWidth="1"/>
-    <col min="8196" max="8196" width="16.3984375" style="3" customWidth="1"/>
-    <col min="8197" max="8197" width="19.69921875" style="3" customWidth="1"/>
+    <col min="8194" max="8194" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="8195" max="8195" width="14.85546875" style="3" customWidth="1"/>
+    <col min="8196" max="8196" width="16.42578125" style="3" customWidth="1"/>
+    <col min="8197" max="8197" width="19.7109375" style="3" customWidth="1"/>
     <col min="8198" max="8449" width="9" style="3"/>
-    <col min="8450" max="8450" width="21.296875" style="3" bestFit="1" customWidth="1"/>
-    <col min="8451" max="8451" width="14.8984375" style="3" customWidth="1"/>
-    <col min="8452" max="8452" width="16.3984375" style="3" customWidth="1"/>
-    <col min="8453" max="8453" width="19.69921875" style="3" customWidth="1"/>
+    <col min="8450" max="8450" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="8451" max="8451" width="14.85546875" style="3" customWidth="1"/>
+    <col min="8452" max="8452" width="16.42578125" style="3" customWidth="1"/>
+    <col min="8453" max="8453" width="19.7109375" style="3" customWidth="1"/>
     <col min="8454" max="8705" width="9" style="3"/>
-    <col min="8706" max="8706" width="21.296875" style="3" bestFit="1" customWidth="1"/>
-    <col min="8707" max="8707" width="14.8984375" style="3" customWidth="1"/>
-    <col min="8708" max="8708" width="16.3984375" style="3" customWidth="1"/>
-    <col min="8709" max="8709" width="19.69921875" style="3" customWidth="1"/>
+    <col min="8706" max="8706" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="8707" max="8707" width="14.85546875" style="3" customWidth="1"/>
+    <col min="8708" max="8708" width="16.42578125" style="3" customWidth="1"/>
+    <col min="8709" max="8709" width="19.7109375" style="3" customWidth="1"/>
     <col min="8710" max="8961" width="9" style="3"/>
-    <col min="8962" max="8962" width="21.296875" style="3" bestFit="1" customWidth="1"/>
-    <col min="8963" max="8963" width="14.8984375" style="3" customWidth="1"/>
-    <col min="8964" max="8964" width="16.3984375" style="3" customWidth="1"/>
-    <col min="8965" max="8965" width="19.69921875" style="3" customWidth="1"/>
+    <col min="8962" max="8962" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="8963" max="8963" width="14.85546875" style="3" customWidth="1"/>
+    <col min="8964" max="8964" width="16.42578125" style="3" customWidth="1"/>
+    <col min="8965" max="8965" width="19.7109375" style="3" customWidth="1"/>
     <col min="8966" max="9217" width="9" style="3"/>
-    <col min="9218" max="9218" width="21.296875" style="3" bestFit="1" customWidth="1"/>
-    <col min="9219" max="9219" width="14.8984375" style="3" customWidth="1"/>
-    <col min="9220" max="9220" width="16.3984375" style="3" customWidth="1"/>
-    <col min="9221" max="9221" width="19.69921875" style="3" customWidth="1"/>
+    <col min="9218" max="9218" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="9219" max="9219" width="14.85546875" style="3" customWidth="1"/>
+    <col min="9220" max="9220" width="16.42578125" style="3" customWidth="1"/>
+    <col min="9221" max="9221" width="19.7109375" style="3" customWidth="1"/>
     <col min="9222" max="9473" width="9" style="3"/>
-    <col min="9474" max="9474" width="21.296875" style="3" bestFit="1" customWidth="1"/>
-    <col min="9475" max="9475" width="14.8984375" style="3" customWidth="1"/>
-    <col min="9476" max="9476" width="16.3984375" style="3" customWidth="1"/>
-    <col min="9477" max="9477" width="19.69921875" style="3" customWidth="1"/>
+    <col min="9474" max="9474" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="9475" max="9475" width="14.85546875" style="3" customWidth="1"/>
+    <col min="9476" max="9476" width="16.42578125" style="3" customWidth="1"/>
+    <col min="9477" max="9477" width="19.7109375" style="3" customWidth="1"/>
     <col min="9478" max="9729" width="9" style="3"/>
-    <col min="9730" max="9730" width="21.296875" style="3" bestFit="1" customWidth="1"/>
-    <col min="9731" max="9731" width="14.8984375" style="3" customWidth="1"/>
-    <col min="9732" max="9732" width="16.3984375" style="3" customWidth="1"/>
-    <col min="9733" max="9733" width="19.69921875" style="3" customWidth="1"/>
+    <col min="9730" max="9730" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="9731" max="9731" width="14.85546875" style="3" customWidth="1"/>
+    <col min="9732" max="9732" width="16.42578125" style="3" customWidth="1"/>
+    <col min="9733" max="9733" width="19.7109375" style="3" customWidth="1"/>
     <col min="9734" max="9985" width="9" style="3"/>
-    <col min="9986" max="9986" width="21.296875" style="3" bestFit="1" customWidth="1"/>
-    <col min="9987" max="9987" width="14.8984375" style="3" customWidth="1"/>
-    <col min="9988" max="9988" width="16.3984375" style="3" customWidth="1"/>
-    <col min="9989" max="9989" width="19.69921875" style="3" customWidth="1"/>
+    <col min="9986" max="9986" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="9987" max="9987" width="14.85546875" style="3" customWidth="1"/>
+    <col min="9988" max="9988" width="16.42578125" style="3" customWidth="1"/>
+    <col min="9989" max="9989" width="19.7109375" style="3" customWidth="1"/>
     <col min="9990" max="10241" width="9" style="3"/>
-    <col min="10242" max="10242" width="21.296875" style="3" bestFit="1" customWidth="1"/>
-    <col min="10243" max="10243" width="14.8984375" style="3" customWidth="1"/>
-    <col min="10244" max="10244" width="16.3984375" style="3" customWidth="1"/>
-    <col min="10245" max="10245" width="19.69921875" style="3" customWidth="1"/>
+    <col min="10242" max="10242" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="10243" max="10243" width="14.85546875" style="3" customWidth="1"/>
+    <col min="10244" max="10244" width="16.42578125" style="3" customWidth="1"/>
+    <col min="10245" max="10245" width="19.7109375" style="3" customWidth="1"/>
     <col min="10246" max="10497" width="9" style="3"/>
-    <col min="10498" max="10498" width="21.296875" style="3" bestFit="1" customWidth="1"/>
-    <col min="10499" max="10499" width="14.8984375" style="3" customWidth="1"/>
-    <col min="10500" max="10500" width="16.3984375" style="3" customWidth="1"/>
-    <col min="10501" max="10501" width="19.69921875" style="3" customWidth="1"/>
+    <col min="10498" max="10498" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="10499" max="10499" width="14.85546875" style="3" customWidth="1"/>
+    <col min="10500" max="10500" width="16.42578125" style="3" customWidth="1"/>
+    <col min="10501" max="10501" width="19.7109375" style="3" customWidth="1"/>
     <col min="10502" max="10753" width="9" style="3"/>
-    <col min="10754" max="10754" width="21.296875" style="3" bestFit="1" customWidth="1"/>
-    <col min="10755" max="10755" width="14.8984375" style="3" customWidth="1"/>
-    <col min="10756" max="10756" width="16.3984375" style="3" customWidth="1"/>
-    <col min="10757" max="10757" width="19.69921875" style="3" customWidth="1"/>
+    <col min="10754" max="10754" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="10755" max="10755" width="14.85546875" style="3" customWidth="1"/>
+    <col min="10756" max="10756" width="16.42578125" style="3" customWidth="1"/>
+    <col min="10757" max="10757" width="19.7109375" style="3" customWidth="1"/>
     <col min="10758" max="11009" width="9" style="3"/>
-    <col min="11010" max="11010" width="21.296875" style="3" bestFit="1" customWidth="1"/>
-    <col min="11011" max="11011" width="14.8984375" style="3" customWidth="1"/>
-    <col min="11012" max="11012" width="16.3984375" style="3" customWidth="1"/>
-    <col min="11013" max="11013" width="19.69921875" style="3" customWidth="1"/>
+    <col min="11010" max="11010" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="11011" max="11011" width="14.85546875" style="3" customWidth="1"/>
+    <col min="11012" max="11012" width="16.42578125" style="3" customWidth="1"/>
+    <col min="11013" max="11013" width="19.7109375" style="3" customWidth="1"/>
     <col min="11014" max="11265" width="9" style="3"/>
-    <col min="11266" max="11266" width="21.296875" style="3" bestFit="1" customWidth="1"/>
-    <col min="11267" max="11267" width="14.8984375" style="3" customWidth="1"/>
-    <col min="11268" max="11268" width="16.3984375" style="3" customWidth="1"/>
-    <col min="11269" max="11269" width="19.69921875" style="3" customWidth="1"/>
+    <col min="11266" max="11266" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="11267" max="11267" width="14.85546875" style="3" customWidth="1"/>
+    <col min="11268" max="11268" width="16.42578125" style="3" customWidth="1"/>
+    <col min="11269" max="11269" width="19.7109375" style="3" customWidth="1"/>
     <col min="11270" max="11521" width="9" style="3"/>
-    <col min="11522" max="11522" width="21.296875" style="3" bestFit="1" customWidth="1"/>
-    <col min="11523" max="11523" width="14.8984375" style="3" customWidth="1"/>
-    <col min="11524" max="11524" width="16.3984375" style="3" customWidth="1"/>
-    <col min="11525" max="11525" width="19.69921875" style="3" customWidth="1"/>
+    <col min="11522" max="11522" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="11523" max="11523" width="14.85546875" style="3" customWidth="1"/>
+    <col min="11524" max="11524" width="16.42578125" style="3" customWidth="1"/>
+    <col min="11525" max="11525" width="19.7109375" style="3" customWidth="1"/>
     <col min="11526" max="11777" width="9" style="3"/>
-    <col min="11778" max="11778" width="21.296875" style="3" bestFit="1" customWidth="1"/>
-    <col min="11779" max="11779" width="14.8984375" style="3" customWidth="1"/>
-    <col min="11780" max="11780" width="16.3984375" style="3" customWidth="1"/>
-    <col min="11781" max="11781" width="19.69921875" style="3" customWidth="1"/>
+    <col min="11778" max="11778" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="11779" max="11779" width="14.85546875" style="3" customWidth="1"/>
+    <col min="11780" max="11780" width="16.42578125" style="3" customWidth="1"/>
+    <col min="11781" max="11781" width="19.7109375" style="3" customWidth="1"/>
     <col min="11782" max="12033" width="9" style="3"/>
-    <col min="12034" max="12034" width="21.296875" style="3" bestFit="1" customWidth="1"/>
-    <col min="12035" max="12035" width="14.8984375" style="3" customWidth="1"/>
-    <col min="12036" max="12036" width="16.3984375" style="3" customWidth="1"/>
-    <col min="12037" max="12037" width="19.69921875" style="3" customWidth="1"/>
+    <col min="12034" max="12034" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="12035" max="12035" width="14.85546875" style="3" customWidth="1"/>
+    <col min="12036" max="12036" width="16.42578125" style="3" customWidth="1"/>
+    <col min="12037" max="12037" width="19.7109375" style="3" customWidth="1"/>
     <col min="12038" max="12289" width="9" style="3"/>
-    <col min="12290" max="12290" width="21.296875" style="3" bestFit="1" customWidth="1"/>
-    <col min="12291" max="12291" width="14.8984375" style="3" customWidth="1"/>
-    <col min="12292" max="12292" width="16.3984375" style="3" customWidth="1"/>
-    <col min="12293" max="12293" width="19.69921875" style="3" customWidth="1"/>
+    <col min="12290" max="12290" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="12291" max="12291" width="14.85546875" style="3" customWidth="1"/>
+    <col min="12292" max="12292" width="16.42578125" style="3" customWidth="1"/>
+    <col min="12293" max="12293" width="19.7109375" style="3" customWidth="1"/>
     <col min="12294" max="12545" width="9" style="3"/>
-    <col min="12546" max="12546" width="21.296875" style="3" bestFit="1" customWidth="1"/>
-    <col min="12547" max="12547" width="14.8984375" style="3" customWidth="1"/>
-    <col min="12548" max="12548" width="16.3984375" style="3" customWidth="1"/>
-    <col min="12549" max="12549" width="19.69921875" style="3" customWidth="1"/>
+    <col min="12546" max="12546" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="12547" max="12547" width="14.85546875" style="3" customWidth="1"/>
+    <col min="12548" max="12548" width="16.42578125" style="3" customWidth="1"/>
+    <col min="12549" max="12549" width="19.7109375" style="3" customWidth="1"/>
     <col min="12550" max="12801" width="9" style="3"/>
-    <col min="12802" max="12802" width="21.296875" style="3" bestFit="1" customWidth="1"/>
-    <col min="12803" max="12803" width="14.8984375" style="3" customWidth="1"/>
-    <col min="12804" max="12804" width="16.3984375" style="3" customWidth="1"/>
-    <col min="12805" max="12805" width="19.69921875" style="3" customWidth="1"/>
+    <col min="12802" max="12802" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="12803" max="12803" width="14.85546875" style="3" customWidth="1"/>
+    <col min="12804" max="12804" width="16.42578125" style="3" customWidth="1"/>
+    <col min="12805" max="12805" width="19.7109375" style="3" customWidth="1"/>
     <col min="12806" max="13057" width="9" style="3"/>
-    <col min="13058" max="13058" width="21.296875" style="3" bestFit="1" customWidth="1"/>
-    <col min="13059" max="13059" width="14.8984375" style="3" customWidth="1"/>
-    <col min="13060" max="13060" width="16.3984375" style="3" customWidth="1"/>
-    <col min="13061" max="13061" width="19.69921875" style="3" customWidth="1"/>
+    <col min="13058" max="13058" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="13059" max="13059" width="14.85546875" style="3" customWidth="1"/>
+    <col min="13060" max="13060" width="16.42578125" style="3" customWidth="1"/>
+    <col min="13061" max="13061" width="19.7109375" style="3" customWidth="1"/>
     <col min="13062" max="13313" width="9" style="3"/>
-    <col min="13314" max="13314" width="21.296875" style="3" bestFit="1" customWidth="1"/>
-    <col min="13315" max="13315" width="14.8984375" style="3" customWidth="1"/>
-    <col min="13316" max="13316" width="16.3984375" style="3" customWidth="1"/>
-    <col min="13317" max="13317" width="19.69921875" style="3" customWidth="1"/>
+    <col min="13314" max="13314" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="13315" max="13315" width="14.85546875" style="3" customWidth="1"/>
+    <col min="13316" max="13316" width="16.42578125" style="3" customWidth="1"/>
+    <col min="13317" max="13317" width="19.7109375" style="3" customWidth="1"/>
     <col min="13318" max="13569" width="9" style="3"/>
-    <col min="13570" max="13570" width="21.296875" style="3" bestFit="1" customWidth="1"/>
-    <col min="13571" max="13571" width="14.8984375" style="3" customWidth="1"/>
-    <col min="13572" max="13572" width="16.3984375" style="3" customWidth="1"/>
-    <col min="13573" max="13573" width="19.69921875" style="3" customWidth="1"/>
+    <col min="13570" max="13570" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="13571" max="13571" width="14.85546875" style="3" customWidth="1"/>
+    <col min="13572" max="13572" width="16.42578125" style="3" customWidth="1"/>
+    <col min="13573" max="13573" width="19.7109375" style="3" customWidth="1"/>
     <col min="13574" max="13825" width="9" style="3"/>
-    <col min="13826" max="13826" width="21.296875" style="3" bestFit="1" customWidth="1"/>
-    <col min="13827" max="13827" width="14.8984375" style="3" customWidth="1"/>
-    <col min="13828" max="13828" width="16.3984375" style="3" customWidth="1"/>
-    <col min="13829" max="13829" width="19.69921875" style="3" customWidth="1"/>
+    <col min="13826" max="13826" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="13827" max="13827" width="14.85546875" style="3" customWidth="1"/>
+    <col min="13828" max="13828" width="16.42578125" style="3" customWidth="1"/>
+    <col min="13829" max="13829" width="19.7109375" style="3" customWidth="1"/>
     <col min="13830" max="14081" width="9" style="3"/>
-    <col min="14082" max="14082" width="21.296875" style="3" bestFit="1" customWidth="1"/>
-    <col min="14083" max="14083" width="14.8984375" style="3" customWidth="1"/>
-    <col min="14084" max="14084" width="16.3984375" style="3" customWidth="1"/>
-    <col min="14085" max="14085" width="19.69921875" style="3" customWidth="1"/>
+    <col min="14082" max="14082" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="14083" max="14083" width="14.85546875" style="3" customWidth="1"/>
+    <col min="14084" max="14084" width="16.42578125" style="3" customWidth="1"/>
+    <col min="14085" max="14085" width="19.7109375" style="3" customWidth="1"/>
     <col min="14086" max="14337" width="9" style="3"/>
-    <col min="14338" max="14338" width="21.296875" style="3" bestFit="1" customWidth="1"/>
-    <col min="14339" max="14339" width="14.8984375" style="3" customWidth="1"/>
-    <col min="14340" max="14340" width="16.3984375" style="3" customWidth="1"/>
-    <col min="14341" max="14341" width="19.69921875" style="3" customWidth="1"/>
+    <col min="14338" max="14338" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="14339" max="14339" width="14.85546875" style="3" customWidth="1"/>
+    <col min="14340" max="14340" width="16.42578125" style="3" customWidth="1"/>
+    <col min="14341" max="14341" width="19.7109375" style="3" customWidth="1"/>
     <col min="14342" max="14593" width="9" style="3"/>
-    <col min="14594" max="14594" width="21.296875" style="3" bestFit="1" customWidth="1"/>
-    <col min="14595" max="14595" width="14.8984375" style="3" customWidth="1"/>
-    <col min="14596" max="14596" width="16.3984375" style="3" customWidth="1"/>
-    <col min="14597" max="14597" width="19.69921875" style="3" customWidth="1"/>
+    <col min="14594" max="14594" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="14595" max="14595" width="14.85546875" style="3" customWidth="1"/>
+    <col min="14596" max="14596" width="16.42578125" style="3" customWidth="1"/>
+    <col min="14597" max="14597" width="19.7109375" style="3" customWidth="1"/>
     <col min="14598" max="14849" width="9" style="3"/>
-    <col min="14850" max="14850" width="21.296875" style="3" bestFit="1" customWidth="1"/>
-    <col min="14851" max="14851" width="14.8984375" style="3" customWidth="1"/>
-    <col min="14852" max="14852" width="16.3984375" style="3" customWidth="1"/>
-    <col min="14853" max="14853" width="19.69921875" style="3" customWidth="1"/>
+    <col min="14850" max="14850" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="14851" max="14851" width="14.85546875" style="3" customWidth="1"/>
+    <col min="14852" max="14852" width="16.42578125" style="3" customWidth="1"/>
+    <col min="14853" max="14853" width="19.7109375" style="3" customWidth="1"/>
     <col min="14854" max="15105" width="9" style="3"/>
-    <col min="15106" max="15106" width="21.296875" style="3" bestFit="1" customWidth="1"/>
-    <col min="15107" max="15107" width="14.8984375" style="3" customWidth="1"/>
-    <col min="15108" max="15108" width="16.3984375" style="3" customWidth="1"/>
-    <col min="15109" max="15109" width="19.69921875" style="3" customWidth="1"/>
+    <col min="15106" max="15106" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="15107" max="15107" width="14.85546875" style="3" customWidth="1"/>
+    <col min="15108" max="15108" width="16.42578125" style="3" customWidth="1"/>
+    <col min="15109" max="15109" width="19.7109375" style="3" customWidth="1"/>
     <col min="15110" max="15361" width="9" style="3"/>
-    <col min="15362" max="15362" width="21.296875" style="3" bestFit="1" customWidth="1"/>
-    <col min="15363" max="15363" width="14.8984375" style="3" customWidth="1"/>
-    <col min="15364" max="15364" width="16.3984375" style="3" customWidth="1"/>
-    <col min="15365" max="15365" width="19.69921875" style="3" customWidth="1"/>
+    <col min="15362" max="15362" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="15363" max="15363" width="14.85546875" style="3" customWidth="1"/>
+    <col min="15364" max="15364" width="16.42578125" style="3" customWidth="1"/>
+    <col min="15365" max="15365" width="19.7109375" style="3" customWidth="1"/>
     <col min="15366" max="15617" width="9" style="3"/>
-    <col min="15618" max="15618" width="21.296875" style="3" bestFit="1" customWidth="1"/>
-    <col min="15619" max="15619" width="14.8984375" style="3" customWidth="1"/>
-    <col min="15620" max="15620" width="16.3984375" style="3" customWidth="1"/>
-    <col min="15621" max="15621" width="19.69921875" style="3" customWidth="1"/>
+    <col min="15618" max="15618" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="15619" max="15619" width="14.85546875" style="3" customWidth="1"/>
+    <col min="15620" max="15620" width="16.42578125" style="3" customWidth="1"/>
+    <col min="15621" max="15621" width="19.7109375" style="3" customWidth="1"/>
     <col min="15622" max="15873" width="9" style="3"/>
-    <col min="15874" max="15874" width="21.296875" style="3" bestFit="1" customWidth="1"/>
-    <col min="15875" max="15875" width="14.8984375" style="3" customWidth="1"/>
-    <col min="15876" max="15876" width="16.3984375" style="3" customWidth="1"/>
-    <col min="15877" max="15877" width="19.69921875" style="3" customWidth="1"/>
+    <col min="15874" max="15874" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="15875" max="15875" width="14.85546875" style="3" customWidth="1"/>
+    <col min="15876" max="15876" width="16.42578125" style="3" customWidth="1"/>
+    <col min="15877" max="15877" width="19.7109375" style="3" customWidth="1"/>
     <col min="15878" max="16129" width="9" style="3"/>
-    <col min="16130" max="16130" width="21.296875" style="3" bestFit="1" customWidth="1"/>
-    <col min="16131" max="16131" width="14.8984375" style="3" customWidth="1"/>
-    <col min="16132" max="16132" width="16.3984375" style="3" customWidth="1"/>
-    <col min="16133" max="16133" width="19.69921875" style="3" customWidth="1"/>
+    <col min="16130" max="16130" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="16131" max="16131" width="14.85546875" style="3" customWidth="1"/>
+    <col min="16132" max="16132" width="16.42578125" style="3" customWidth="1"/>
+    <col min="16133" max="16133" width="19.7109375" style="3" customWidth="1"/>
     <col min="16134" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="21.6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:5" ht="20.25">
       <c r="A1" s="15" t="s">
         <v>14</v>
       </c>
@@ -2418,14 +2415,14 @@
       <c r="D1" s="15"/>
       <c r="E1" s="15"/>
     </row>
-    <row r="2" spans="1:5" ht="21.6" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:5" ht="20.25">
       <c r="A2" s="4"/>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:5">
       <c r="A4" s="5" t="s">
         <v>15</v>
       </c>
@@ -2442,7 +2439,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:5">
       <c r="A5" s="6">
         <v>1</v>
       </c>
@@ -2451,7 +2448,7 @@
       <c r="D5" s="6"/>
       <c r="E5" s="6"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:5">
       <c r="A6" s="6">
         <v>2</v>
       </c>
@@ -2460,7 +2457,7 @@
       <c r="D6" s="6"/>
       <c r="E6" s="6"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:5">
       <c r="A7" s="6">
         <v>3</v>
       </c>
@@ -2469,175 +2466,175 @@
       <c r="D7" s="6"/>
       <c r="E7" s="6"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:5">
       <c r="A8" s="6"/>
       <c r="B8" s="6"/>
       <c r="C8" s="6"/>
       <c r="D8" s="6"/>
       <c r="E8" s="6"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:5">
       <c r="A9" s="6"/>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
       <c r="D9" s="6"/>
       <c r="E9" s="6"/>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:5">
       <c r="A10" s="6"/>
       <c r="B10" s="6"/>
       <c r="C10" s="6"/>
       <c r="D10" s="6"/>
       <c r="E10" s="6"/>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:5">
       <c r="A11" s="6"/>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
       <c r="D11" s="6"/>
       <c r="E11" s="6"/>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:5">
       <c r="A12" s="6"/>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
       <c r="D12" s="6"/>
       <c r="E12" s="6"/>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:5">
       <c r="A13" s="6"/>
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
       <c r="E13" s="6"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:5">
       <c r="A14" s="6"/>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
       <c r="D14" s="6"/>
       <c r="E14" s="6"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:5">
       <c r="A15" s="6"/>
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
       <c r="E15" s="6"/>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:5">
       <c r="A16" s="6"/>
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
       <c r="D16" s="6"/>
       <c r="E16" s="6"/>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:5">
       <c r="A17" s="6"/>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
       <c r="D17" s="6"/>
       <c r="E17" s="6"/>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:5">
       <c r="A18" s="6"/>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
       <c r="D18" s="6"/>
       <c r="E18" s="6"/>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:5">
       <c r="A19" s="6"/>
       <c r="B19" s="6"/>
       <c r="C19" s="6"/>
       <c r="D19" s="6"/>
       <c r="E19" s="6"/>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:5">
       <c r="A20" s="6"/>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
       <c r="D20" s="6"/>
       <c r="E20" s="6"/>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:5">
       <c r="A21" s="6"/>
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
       <c r="D21" s="6"/>
       <c r="E21" s="6"/>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:5">
       <c r="A22" s="6"/>
       <c r="B22" s="6"/>
       <c r="C22" s="6"/>
       <c r="D22" s="6"/>
       <c r="E22" s="6"/>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:5">
       <c r="A23" s="6"/>
       <c r="B23" s="6"/>
       <c r="C23" s="6"/>
       <c r="D23" s="6"/>
       <c r="E23" s="6"/>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:5">
       <c r="A24" s="6"/>
       <c r="B24" s="6"/>
       <c r="C24" s="6"/>
       <c r="D24" s="6"/>
       <c r="E24" s="6"/>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:5">
       <c r="A25" s="6"/>
       <c r="B25" s="6"/>
       <c r="C25" s="6"/>
       <c r="D25" s="6"/>
       <c r="E25" s="6"/>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:5">
       <c r="A26" s="6"/>
       <c r="B26" s="6"/>
       <c r="C26" s="6"/>
       <c r="D26" s="6"/>
       <c r="E26" s="6"/>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:5">
       <c r="A27" s="6"/>
       <c r="B27" s="6"/>
       <c r="C27" s="6"/>
       <c r="D27" s="6"/>
       <c r="E27" s="6"/>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:5">
       <c r="A28" s="6"/>
       <c r="B28" s="6"/>
       <c r="C28" s="6"/>
       <c r="D28" s="6"/>
       <c r="E28" s="6"/>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:5">
       <c r="A29" s="6"/>
       <c r="B29" s="6"/>
       <c r="C29" s="6"/>
       <c r="D29" s="6"/>
       <c r="E29" s="6"/>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:5">
       <c r="A30" s="6"/>
       <c r="B30" s="6"/>
       <c r="C30" s="6"/>
       <c r="D30" s="6"/>
       <c r="E30" s="6"/>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:5">
       <c r="A31" s="6"/>
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
       <c r="D31" s="6"/>
       <c r="E31" s="6"/>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:5">
       <c r="A32" s="6"/>
       <c r="B32" s="6"/>
       <c r="C32" s="6"/>
@@ -2650,7 +2647,7 @@
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <dataValidations xWindow="335" yWindow="435" count="1">
-    <dataValidation type="textLength" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="부서ID는 회사ID 및 개인ID와 중복되지 않은 것으로서 _x000a_3~9자리의 영문,숫자의 조합으로 만듭니다._x000a_" sqref="C1:C1048576" xr:uid="{00000000-0002-0000-0300-000000000000}">
+    <dataValidation type="textLength" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="부서ID는 회사ID 및 개인ID와 중복되지 않은 것으로서 _x000a_3~9자리의 영문,숫자의 조합으로 만듭니다._x000a_" sqref="C1:C1048576">
       <formula1>3</formula1>
       <formula2>9</formula2>
     </dataValidation>

--- a/docs/tech/조직도 등록메뉴얼.xlsx
+++ b/docs/tech/조직도 등록메뉴얼.xlsx
@@ -305,10 +305,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>직위순서</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>① 모든 ID생성시 최소3자리 최대20자리의 글자수제한이 있다.</t>
   </si>
   <si>
@@ -320,6 +316,9 @@
   </si>
   <si>
     <t>⑤ 이동전화 입력시 000-0000-0000 형식으로 입력</t>
+  </si>
+  <si>
+    <t>부서내 순서</t>
   </si>
 </sst>
 </file>
@@ -1119,7 +1118,7 @@
         <xdr:cNvPr id="2" name="그림 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1179,7 +1178,7 @@
         <xdr:cNvPr id="3" name="그림 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000003000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1505,7 +1504,7 @@
         <v>70</v>
       </c>
       <c r="J5" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6" spans="2:11">
@@ -1537,7 +1536,7 @@
         <v>73</v>
       </c>
       <c r="J9" s="10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10" spans="2:11">
@@ -1545,7 +1544,7 @@
         <v>74</v>
       </c>
       <c r="J10" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="11" spans="2:11">
@@ -1610,8 +1609,10 @@
     <col min="6" max="6" width="15.140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.42578125" customWidth="1"/>
     <col min="12" max="12" width="10.42578125" customWidth="1"/>
     <col min="14" max="14" width="11.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.42578125" customWidth="1"/>
     <col min="16" max="16" width="13.42578125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
   </cols>
@@ -1648,13 +1649,13 @@
         <v>9</v>
       </c>
       <c r="K1" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="L1" t="s">
         <v>20</v>
       </c>
       <c r="M1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N1" s="2" t="s">
         <v>10</v>

--- a/docs/tech/조직도 등록메뉴얼.xlsx
+++ b/docs/tech/조직도 등록메뉴얼.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="15" windowWidth="29040" windowHeight="16440"/>
+    <workbookView xWindow="28680" yWindow="15" windowWidth="29040" windowHeight="16440" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="작성시유의사항" sheetId="2" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="81">
   <si>
     <t>순서</t>
   </si>
@@ -319,6 +319,9 @@
   </si>
   <si>
     <t>부서내 순서</t>
+  </si>
+  <si>
+    <t>이메일주소</t>
   </si>
 </sst>
 </file>
@@ -1118,7 +1121,7 @@
         <xdr:cNvPr id="2" name="그림 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1178,7 +1181,7 @@
         <xdr:cNvPr id="3" name="그림 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1600,7 +1603,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:R2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="13" bestFit="1" customWidth="1"/>
@@ -1615,9 +1618,10 @@
     <col min="15" max="15" width="11.42578125" customWidth="1"/>
     <col min="16" max="16" width="13.42578125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:18">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1669,8 +1673,11 @@
       <c r="Q1" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:17">
+      <c r="R1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18">
       <c r="A2">
         <v>1</v>
       </c>

--- a/docs/tech/조직도 등록메뉴얼.xlsx
+++ b/docs/tech/조직도 등록메뉴얼.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr/>
+  <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Projects\kaoni\jmocha\ezFlow4Java\docs\tech\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\dev\workspace\ezFlow4Java\docs\tech\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="15" windowWidth="29040" windowHeight="16440" activeTab="1"/>
+    <workbookView xWindow="28680" yWindow="15" windowWidth="29040" windowHeight="16440"/>
   </bookViews>
   <sheets>
     <sheet name="작성시유의사항" sheetId="2" r:id="rId1"/>
@@ -17,7 +17,7 @@
     <sheet name="예시" sheetId="4" state="hidden" r:id="rId3"/>
     <sheet name="부서정보" sheetId="3" state="hidden" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="85">
   <si>
     <t>순서</t>
   </si>
@@ -241,10 +241,6 @@
     <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">    (이때, E,F열은 입력하지 않는다.)</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">    (이때, dept파트에 G~O열이 입력되어 있거나, user파트에 E~F열이 입력되어있으면 안된다.)</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -265,78 +261,98 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
+    <t>양력</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>음력</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>③ 비밀번호는 8~12자리로 숫자,영문,특수문자의 조합으로 생성한다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>tomato</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 부서정보를 C2:Fn 열에 입력한다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>② 부서정보가 입력되었으면, 바로 아래행부터 직원정보를 입력한다</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>③ G열에 직원이름을 입력한 후, C,D열에 각각 직원별 부서와 그 부서ID를 입력한다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>④ H열 부터 O열까지 각 사용자별 정보를 입력한다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>⑤ B2셀을 셀이 입력된 곳 까지 채우기핸들을 사용하여 아래로 드래그한다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 모든 ID생성시 최소3자리 최대20자리의 글자수제한이 있다.</t>
+  </si>
+  <si>
+    <t>사번</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>④ 생년월일 입력시 0000-00-00 형식으로 입력</t>
+  </si>
+  <si>
+    <t>⑤ 이동전화 입력시 000-0000-0000 형식으로 입력</t>
+  </si>
+  <si>
+    <t>부서내 순서</t>
+  </si>
+  <si>
+    <t>이메일주소</t>
+  </si>
+  <si>
     <t>⑦ 필수입력정보 : 부서명/부서아이디/상위부서명/상위부서아이디/이름/아이디/비밀번호</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>양력</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>음력</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>③ 비밀번호는 8~12자리로 숫자,영문,특수문자의 조합으로 생성한다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>tomato</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>① 부서정보를 C2:Fn 열에 입력한다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>② 부서정보가 입력되었으면, 바로 아래행부터 직원정보를 입력한다</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>③ G열에 직원이름을 입력한 후, C,D열에 각각 직원별 부서와 그 부서ID를 입력한다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>④ H열 부터 O열까지 각 사용자별 정보를 입력한다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>⑤ B2셀을 셀이 입력된 곳 까지 채우기핸들을 사용하여 아래로 드래그한다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>① 모든 ID생성시 최소3자리 최대20자리의 글자수제한이 있다.</t>
-  </si>
-  <si>
-    <t>사번</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>④ 생년월일 입력시 0000-00-00 형식으로 입력</t>
-  </si>
-  <si>
-    <t>⑤ 이동전화 입력시 000-0000-0000 형식으로 입력</t>
-  </si>
-  <si>
-    <t>부서내 순서</t>
-  </si>
-  <si>
-    <t>이메일주소</t>
+    <t xml:space="preserve">    (이때, E,F열은 입력하지 않는다.)</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">        (naver.com 같은 외부 메일 주소가 아니라 도메인은 같고 아이디가 다른 경우)</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">    부서는 이메일주소 컬럼을 사용하지 않으며 ID@도메인으로 고정된다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">    유저의 아이디와 이메일 아이디를 다르게 쓰려면 ID@도메인 형식으로 입력한다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>⑧ 이메일주소 : 값이 비었을 때는 이메일 주소가 자동으로 ID@도메인으로 설정된다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="000\-0000\-0000"/>
-    <numFmt numFmtId="165" formatCode="\1\900\-00\-00"/>
+    <numFmt numFmtId="176" formatCode="000\-0000\-0000"/>
+    <numFmt numFmtId="177" formatCode="\1\900\-00\-00"/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -344,7 +360,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -352,7 +368,7 @@
     <font>
       <sz val="18"/>
       <color theme="3"/>
-      <name val="Calibri Light"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="major"/>
@@ -361,7 +377,7 @@
       <b/>
       <sz val="15"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -370,7 +386,7 @@
       <b/>
       <sz val="13"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -379,7 +395,7 @@
       <b/>
       <sz val="11"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -387,7 +403,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -395,7 +411,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -403,7 +419,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -411,7 +427,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -420,7 +436,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -429,7 +445,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -437,7 +453,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -446,7 +462,7 @@
       <b/>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -454,7 +470,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -463,7 +479,7 @@
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -472,7 +488,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -480,14 +496,14 @@
     <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -495,7 +511,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -532,7 +548,7 @@
     <font>
       <sz val="15"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -540,7 +556,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -998,14 +1014,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
@@ -1042,6 +1058,9 @@
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1106,22 +1125,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>19755</xdr:rowOff>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>162630</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>524889</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
+      <xdr:colOff>534414</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="그림 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1143,7 +1162,7 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="0" y="2839155"/>
+          <a:off x="9525" y="3610680"/>
           <a:ext cx="10392789" cy="4295070"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1167,21 +1186,21 @@
     <xdr:from>
       <xdr:col>14</xdr:col>
       <xdr:colOff>647701</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>161924</xdr:rowOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>85724</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
       <xdr:colOff>602335</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>76199</xdr:rowOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>209549</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="그림 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000003000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1203,7 +1222,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10515601" y="3190874"/>
+          <a:off x="10515601" y="3533774"/>
           <a:ext cx="2697834" cy="3362325"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1480,116 +1499,130 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B3:S42"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.28515625" style="10" customWidth="1"/>
-    <col min="2" max="2" width="12.28515625" style="10" customWidth="1"/>
-    <col min="3" max="3" width="11.140625" style="10" customWidth="1"/>
+    <col min="1" max="1" width="4.25" style="10" customWidth="1"/>
+    <col min="2" max="2" width="12.25" style="10" customWidth="1"/>
+    <col min="3" max="3" width="11.125" style="10" customWidth="1"/>
     <col min="4" max="8" width="9" style="10"/>
-    <col min="9" max="9" width="11.85546875" style="10" customWidth="1"/>
+    <col min="9" max="9" width="11.875" style="10" customWidth="1"/>
     <col min="10" max="16384" width="9" style="10"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:11" s="8" customFormat="1" ht="24">
+    <row r="3" spans="2:11" s="8" customFormat="1" ht="24" x14ac:dyDescent="0.3">
       <c r="B3" s="7" t="s">
         <v>58</v>
       </c>
       <c r="J3" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="K3" s="7"/>
+    </row>
+    <row r="4" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B4" s="9"/>
+    </row>
+    <row r="5" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B5" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="J5" s="10" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B6" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="J6" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="K3" s="7"/>
-    </row>
-    <row r="4" spans="2:11">
-      <c r="B4" s="9"/>
-    </row>
-    <row r="5" spans="2:11">
-      <c r="B5" s="9" t="s">
+    </row>
+    <row r="7" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B7" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="J5" s="10" t="s">
+      <c r="J7" s="10" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="8" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B8" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="J8" s="10" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="9" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B9" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="J9" s="10" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="6" spans="2:11">
-      <c r="B6" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="J6" s="10" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="7" spans="2:11">
-      <c r="B7" s="11" t="s">
+    <row r="10" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B10" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="J7" s="10" t="s">
+      <c r="J10" s="10" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="11" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B11" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="J11" s="10" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="8" spans="2:11">
-      <c r="B8" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="J8" s="10" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="9" spans="2:11">
-      <c r="B9" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="J9" s="10" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="10" spans="2:11">
-      <c r="B10" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="J10" s="10" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="11" spans="2:11">
-      <c r="B11" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="J11" s="10" t="s">
+    <row r="12" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="J12" s="16" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="13" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B13" s="11"/>
+      <c r="J13" s="16" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="14" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B14" s="11"/>
+      <c r="J14" s="10" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="15" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B15" s="11"/>
+      <c r="J15" s="10" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="16" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="J16" s="10" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="18" spans="2:19" ht="24" x14ac:dyDescent="0.3">
+      <c r="S18" s="7"/>
+    </row>
+    <row r="32" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B32" s="12"/>
+    </row>
+    <row r="35" spans="2:3" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B35" s="14" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="12" spans="2:11">
-      <c r="J12" s="10" t="s">
+    <row r="36" spans="2:3" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B36" s="14" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="13" spans="2:11">
-      <c r="B13" s="11"/>
-    </row>
-    <row r="14" spans="2:11">
-      <c r="B14" s="11"/>
-    </row>
-    <row r="15" spans="2:11">
-      <c r="B15" s="11"/>
-    </row>
-    <row r="18" spans="2:19" ht="24">
-      <c r="S18" s="7"/>
-    </row>
-    <row r="32" spans="2:19">
-      <c r="B32" s="12"/>
-    </row>
-    <row r="35" spans="2:3" hidden="1">
-      <c r="B35" s="14" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="36" spans="2:3" hidden="1">
-      <c r="B36" s="14" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="37" spans="2:3" hidden="1"/>
-    <row r="42" spans="2:3">
+    <row r="37" spans="2:3" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="42" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B42" s="13"/>
       <c r="C42" s="13"/>
     </row>
@@ -1604,24 +1637,24 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:R2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="13" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.42578125" customWidth="1"/>
-    <col min="12" max="12" width="10.42578125" customWidth="1"/>
-    <col min="14" max="14" width="11.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.42578125" customWidth="1"/>
-    <col min="16" max="16" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="12.5703125" customWidth="1"/>
+    <col min="11" max="11" width="13.375" customWidth="1"/>
+    <col min="12" max="12" width="10.375" customWidth="1"/>
+    <col min="14" max="14" width="11.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.375" customWidth="1"/>
+    <col min="16" max="16" width="13.375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1653,13 +1686,13 @@
         <v>9</v>
       </c>
       <c r="K1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="L1" t="s">
         <v>20</v>
       </c>
       <c r="M1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="N1" s="2" t="s">
         <v>10</v>
@@ -1674,10 +1707,10 @@
         <v>13</v>
       </c>
       <c r="R1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1722,21 +1755,21 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:O10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="13" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.42578125" customWidth="1"/>
-    <col min="12" max="12" width="11.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.375" customWidth="1"/>
+    <col min="12" max="12" width="11.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.375" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1783,7 +1816,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1804,7 +1837,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1825,7 +1858,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1846,7 +1879,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1867,7 +1900,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1888,7 +1921,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1927,7 +1960,7 @@
         <v>1056235623</v>
       </c>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1948,7 +1981,7 @@
         <v>49</v>
       </c>
       <c r="I8" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="J8" t="s">
         <v>50</v>
@@ -1966,7 +1999,7 @@
         <v>1089568956</v>
       </c>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2005,7 +2038,7 @@
         <v>1045124512</v>
       </c>
     </row>
-    <row r="10" spans="1:15">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2089,332 +2122,332 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E32"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
-    <col min="2" max="2" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.85546875" style="3" customWidth="1"/>
-    <col min="4" max="4" width="16.42578125" style="3" customWidth="1"/>
-    <col min="5" max="5" width="19.7109375" style="3" customWidth="1"/>
+    <col min="2" max="2" width="21.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.875" style="3" customWidth="1"/>
+    <col min="4" max="4" width="16.375" style="3" customWidth="1"/>
+    <col min="5" max="5" width="19.75" style="3" customWidth="1"/>
     <col min="6" max="257" width="9" style="3"/>
-    <col min="258" max="258" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="259" max="259" width="14.85546875" style="3" customWidth="1"/>
-    <col min="260" max="260" width="16.42578125" style="3" customWidth="1"/>
-    <col min="261" max="261" width="19.7109375" style="3" customWidth="1"/>
+    <col min="258" max="258" width="21.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="259" max="259" width="14.875" style="3" customWidth="1"/>
+    <col min="260" max="260" width="16.375" style="3" customWidth="1"/>
+    <col min="261" max="261" width="19.75" style="3" customWidth="1"/>
     <col min="262" max="513" width="9" style="3"/>
-    <col min="514" max="514" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="515" max="515" width="14.85546875" style="3" customWidth="1"/>
-    <col min="516" max="516" width="16.42578125" style="3" customWidth="1"/>
-    <col min="517" max="517" width="19.7109375" style="3" customWidth="1"/>
+    <col min="514" max="514" width="21.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="515" max="515" width="14.875" style="3" customWidth="1"/>
+    <col min="516" max="516" width="16.375" style="3" customWidth="1"/>
+    <col min="517" max="517" width="19.75" style="3" customWidth="1"/>
     <col min="518" max="769" width="9" style="3"/>
-    <col min="770" max="770" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="771" max="771" width="14.85546875" style="3" customWidth="1"/>
-    <col min="772" max="772" width="16.42578125" style="3" customWidth="1"/>
-    <col min="773" max="773" width="19.7109375" style="3" customWidth="1"/>
+    <col min="770" max="770" width="21.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="771" max="771" width="14.875" style="3" customWidth="1"/>
+    <col min="772" max="772" width="16.375" style="3" customWidth="1"/>
+    <col min="773" max="773" width="19.75" style="3" customWidth="1"/>
     <col min="774" max="1025" width="9" style="3"/>
-    <col min="1026" max="1026" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="1027" max="1027" width="14.85546875" style="3" customWidth="1"/>
-    <col min="1028" max="1028" width="16.42578125" style="3" customWidth="1"/>
-    <col min="1029" max="1029" width="19.7109375" style="3" customWidth="1"/>
+    <col min="1026" max="1026" width="21.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="1027" max="1027" width="14.875" style="3" customWidth="1"/>
+    <col min="1028" max="1028" width="16.375" style="3" customWidth="1"/>
+    <col min="1029" max="1029" width="19.75" style="3" customWidth="1"/>
     <col min="1030" max="1281" width="9" style="3"/>
-    <col min="1282" max="1282" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="1283" max="1283" width="14.85546875" style="3" customWidth="1"/>
-    <col min="1284" max="1284" width="16.42578125" style="3" customWidth="1"/>
-    <col min="1285" max="1285" width="19.7109375" style="3" customWidth="1"/>
+    <col min="1282" max="1282" width="21.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="1283" max="1283" width="14.875" style="3" customWidth="1"/>
+    <col min="1284" max="1284" width="16.375" style="3" customWidth="1"/>
+    <col min="1285" max="1285" width="19.75" style="3" customWidth="1"/>
     <col min="1286" max="1537" width="9" style="3"/>
-    <col min="1538" max="1538" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="1539" max="1539" width="14.85546875" style="3" customWidth="1"/>
-    <col min="1540" max="1540" width="16.42578125" style="3" customWidth="1"/>
-    <col min="1541" max="1541" width="19.7109375" style="3" customWidth="1"/>
+    <col min="1538" max="1538" width="21.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="1539" max="1539" width="14.875" style="3" customWidth="1"/>
+    <col min="1540" max="1540" width="16.375" style="3" customWidth="1"/>
+    <col min="1541" max="1541" width="19.75" style="3" customWidth="1"/>
     <col min="1542" max="1793" width="9" style="3"/>
-    <col min="1794" max="1794" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="1795" max="1795" width="14.85546875" style="3" customWidth="1"/>
-    <col min="1796" max="1796" width="16.42578125" style="3" customWidth="1"/>
-    <col min="1797" max="1797" width="19.7109375" style="3" customWidth="1"/>
+    <col min="1794" max="1794" width="21.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="1795" max="1795" width="14.875" style="3" customWidth="1"/>
+    <col min="1796" max="1796" width="16.375" style="3" customWidth="1"/>
+    <col min="1797" max="1797" width="19.75" style="3" customWidth="1"/>
     <col min="1798" max="2049" width="9" style="3"/>
-    <col min="2050" max="2050" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="2051" max="2051" width="14.85546875" style="3" customWidth="1"/>
-    <col min="2052" max="2052" width="16.42578125" style="3" customWidth="1"/>
-    <col min="2053" max="2053" width="19.7109375" style="3" customWidth="1"/>
+    <col min="2050" max="2050" width="21.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="2051" max="2051" width="14.875" style="3" customWidth="1"/>
+    <col min="2052" max="2052" width="16.375" style="3" customWidth="1"/>
+    <col min="2053" max="2053" width="19.75" style="3" customWidth="1"/>
     <col min="2054" max="2305" width="9" style="3"/>
-    <col min="2306" max="2306" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="2307" max="2307" width="14.85546875" style="3" customWidth="1"/>
-    <col min="2308" max="2308" width="16.42578125" style="3" customWidth="1"/>
-    <col min="2309" max="2309" width="19.7109375" style="3" customWidth="1"/>
+    <col min="2306" max="2306" width="21.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="2307" max="2307" width="14.875" style="3" customWidth="1"/>
+    <col min="2308" max="2308" width="16.375" style="3" customWidth="1"/>
+    <col min="2309" max="2309" width="19.75" style="3" customWidth="1"/>
     <col min="2310" max="2561" width="9" style="3"/>
-    <col min="2562" max="2562" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="2563" max="2563" width="14.85546875" style="3" customWidth="1"/>
-    <col min="2564" max="2564" width="16.42578125" style="3" customWidth="1"/>
-    <col min="2565" max="2565" width="19.7109375" style="3" customWidth="1"/>
+    <col min="2562" max="2562" width="21.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="2563" max="2563" width="14.875" style="3" customWidth="1"/>
+    <col min="2564" max="2564" width="16.375" style="3" customWidth="1"/>
+    <col min="2565" max="2565" width="19.75" style="3" customWidth="1"/>
     <col min="2566" max="2817" width="9" style="3"/>
-    <col min="2818" max="2818" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="2819" max="2819" width="14.85546875" style="3" customWidth="1"/>
-    <col min="2820" max="2820" width="16.42578125" style="3" customWidth="1"/>
-    <col min="2821" max="2821" width="19.7109375" style="3" customWidth="1"/>
+    <col min="2818" max="2818" width="21.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="2819" max="2819" width="14.875" style="3" customWidth="1"/>
+    <col min="2820" max="2820" width="16.375" style="3" customWidth="1"/>
+    <col min="2821" max="2821" width="19.75" style="3" customWidth="1"/>
     <col min="2822" max="3073" width="9" style="3"/>
-    <col min="3074" max="3074" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="3075" max="3075" width="14.85546875" style="3" customWidth="1"/>
-    <col min="3076" max="3076" width="16.42578125" style="3" customWidth="1"/>
-    <col min="3077" max="3077" width="19.7109375" style="3" customWidth="1"/>
+    <col min="3074" max="3074" width="21.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="3075" max="3075" width="14.875" style="3" customWidth="1"/>
+    <col min="3076" max="3076" width="16.375" style="3" customWidth="1"/>
+    <col min="3077" max="3077" width="19.75" style="3" customWidth="1"/>
     <col min="3078" max="3329" width="9" style="3"/>
-    <col min="3330" max="3330" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="3331" max="3331" width="14.85546875" style="3" customWidth="1"/>
-    <col min="3332" max="3332" width="16.42578125" style="3" customWidth="1"/>
-    <col min="3333" max="3333" width="19.7109375" style="3" customWidth="1"/>
+    <col min="3330" max="3330" width="21.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="3331" max="3331" width="14.875" style="3" customWidth="1"/>
+    <col min="3332" max="3332" width="16.375" style="3" customWidth="1"/>
+    <col min="3333" max="3333" width="19.75" style="3" customWidth="1"/>
     <col min="3334" max="3585" width="9" style="3"/>
-    <col min="3586" max="3586" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="3587" max="3587" width="14.85546875" style="3" customWidth="1"/>
-    <col min="3588" max="3588" width="16.42578125" style="3" customWidth="1"/>
-    <col min="3589" max="3589" width="19.7109375" style="3" customWidth="1"/>
+    <col min="3586" max="3586" width="21.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="3587" max="3587" width="14.875" style="3" customWidth="1"/>
+    <col min="3588" max="3588" width="16.375" style="3" customWidth="1"/>
+    <col min="3589" max="3589" width="19.75" style="3" customWidth="1"/>
     <col min="3590" max="3841" width="9" style="3"/>
-    <col min="3842" max="3842" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="3843" max="3843" width="14.85546875" style="3" customWidth="1"/>
-    <col min="3844" max="3844" width="16.42578125" style="3" customWidth="1"/>
-    <col min="3845" max="3845" width="19.7109375" style="3" customWidth="1"/>
+    <col min="3842" max="3842" width="21.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="3843" max="3843" width="14.875" style="3" customWidth="1"/>
+    <col min="3844" max="3844" width="16.375" style="3" customWidth="1"/>
+    <col min="3845" max="3845" width="19.75" style="3" customWidth="1"/>
     <col min="3846" max="4097" width="9" style="3"/>
-    <col min="4098" max="4098" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="4099" max="4099" width="14.85546875" style="3" customWidth="1"/>
-    <col min="4100" max="4100" width="16.42578125" style="3" customWidth="1"/>
-    <col min="4101" max="4101" width="19.7109375" style="3" customWidth="1"/>
+    <col min="4098" max="4098" width="21.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="4099" max="4099" width="14.875" style="3" customWidth="1"/>
+    <col min="4100" max="4100" width="16.375" style="3" customWidth="1"/>
+    <col min="4101" max="4101" width="19.75" style="3" customWidth="1"/>
     <col min="4102" max="4353" width="9" style="3"/>
-    <col min="4354" max="4354" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="4355" max="4355" width="14.85546875" style="3" customWidth="1"/>
-    <col min="4356" max="4356" width="16.42578125" style="3" customWidth="1"/>
-    <col min="4357" max="4357" width="19.7109375" style="3" customWidth="1"/>
+    <col min="4354" max="4354" width="21.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="4355" max="4355" width="14.875" style="3" customWidth="1"/>
+    <col min="4356" max="4356" width="16.375" style="3" customWidth="1"/>
+    <col min="4357" max="4357" width="19.75" style="3" customWidth="1"/>
     <col min="4358" max="4609" width="9" style="3"/>
-    <col min="4610" max="4610" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="4611" max="4611" width="14.85546875" style="3" customWidth="1"/>
-    <col min="4612" max="4612" width="16.42578125" style="3" customWidth="1"/>
-    <col min="4613" max="4613" width="19.7109375" style="3" customWidth="1"/>
+    <col min="4610" max="4610" width="21.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="4611" max="4611" width="14.875" style="3" customWidth="1"/>
+    <col min="4612" max="4612" width="16.375" style="3" customWidth="1"/>
+    <col min="4613" max="4613" width="19.75" style="3" customWidth="1"/>
     <col min="4614" max="4865" width="9" style="3"/>
-    <col min="4866" max="4866" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="4867" max="4867" width="14.85546875" style="3" customWidth="1"/>
-    <col min="4868" max="4868" width="16.42578125" style="3" customWidth="1"/>
-    <col min="4869" max="4869" width="19.7109375" style="3" customWidth="1"/>
+    <col min="4866" max="4866" width="21.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="4867" max="4867" width="14.875" style="3" customWidth="1"/>
+    <col min="4868" max="4868" width="16.375" style="3" customWidth="1"/>
+    <col min="4869" max="4869" width="19.75" style="3" customWidth="1"/>
     <col min="4870" max="5121" width="9" style="3"/>
-    <col min="5122" max="5122" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="5123" max="5123" width="14.85546875" style="3" customWidth="1"/>
-    <col min="5124" max="5124" width="16.42578125" style="3" customWidth="1"/>
-    <col min="5125" max="5125" width="19.7109375" style="3" customWidth="1"/>
+    <col min="5122" max="5122" width="21.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="5123" max="5123" width="14.875" style="3" customWidth="1"/>
+    <col min="5124" max="5124" width="16.375" style="3" customWidth="1"/>
+    <col min="5125" max="5125" width="19.75" style="3" customWidth="1"/>
     <col min="5126" max="5377" width="9" style="3"/>
-    <col min="5378" max="5378" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="5379" max="5379" width="14.85546875" style="3" customWidth="1"/>
-    <col min="5380" max="5380" width="16.42578125" style="3" customWidth="1"/>
-    <col min="5381" max="5381" width="19.7109375" style="3" customWidth="1"/>
+    <col min="5378" max="5378" width="21.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="5379" max="5379" width="14.875" style="3" customWidth="1"/>
+    <col min="5380" max="5380" width="16.375" style="3" customWidth="1"/>
+    <col min="5381" max="5381" width="19.75" style="3" customWidth="1"/>
     <col min="5382" max="5633" width="9" style="3"/>
-    <col min="5634" max="5634" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="5635" max="5635" width="14.85546875" style="3" customWidth="1"/>
-    <col min="5636" max="5636" width="16.42578125" style="3" customWidth="1"/>
-    <col min="5637" max="5637" width="19.7109375" style="3" customWidth="1"/>
+    <col min="5634" max="5634" width="21.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="5635" max="5635" width="14.875" style="3" customWidth="1"/>
+    <col min="5636" max="5636" width="16.375" style="3" customWidth="1"/>
+    <col min="5637" max="5637" width="19.75" style="3" customWidth="1"/>
     <col min="5638" max="5889" width="9" style="3"/>
-    <col min="5890" max="5890" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="5891" max="5891" width="14.85546875" style="3" customWidth="1"/>
-    <col min="5892" max="5892" width="16.42578125" style="3" customWidth="1"/>
-    <col min="5893" max="5893" width="19.7109375" style="3" customWidth="1"/>
+    <col min="5890" max="5890" width="21.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="5891" max="5891" width="14.875" style="3" customWidth="1"/>
+    <col min="5892" max="5892" width="16.375" style="3" customWidth="1"/>
+    <col min="5893" max="5893" width="19.75" style="3" customWidth="1"/>
     <col min="5894" max="6145" width="9" style="3"/>
-    <col min="6146" max="6146" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="6147" max="6147" width="14.85546875" style="3" customWidth="1"/>
-    <col min="6148" max="6148" width="16.42578125" style="3" customWidth="1"/>
-    <col min="6149" max="6149" width="19.7109375" style="3" customWidth="1"/>
+    <col min="6146" max="6146" width="21.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="6147" max="6147" width="14.875" style="3" customWidth="1"/>
+    <col min="6148" max="6148" width="16.375" style="3" customWidth="1"/>
+    <col min="6149" max="6149" width="19.75" style="3" customWidth="1"/>
     <col min="6150" max="6401" width="9" style="3"/>
-    <col min="6402" max="6402" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="6403" max="6403" width="14.85546875" style="3" customWidth="1"/>
-    <col min="6404" max="6404" width="16.42578125" style="3" customWidth="1"/>
-    <col min="6405" max="6405" width="19.7109375" style="3" customWidth="1"/>
+    <col min="6402" max="6402" width="21.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="6403" max="6403" width="14.875" style="3" customWidth="1"/>
+    <col min="6404" max="6404" width="16.375" style="3" customWidth="1"/>
+    <col min="6405" max="6405" width="19.75" style="3" customWidth="1"/>
     <col min="6406" max="6657" width="9" style="3"/>
-    <col min="6658" max="6658" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="6659" max="6659" width="14.85546875" style="3" customWidth="1"/>
-    <col min="6660" max="6660" width="16.42578125" style="3" customWidth="1"/>
-    <col min="6661" max="6661" width="19.7109375" style="3" customWidth="1"/>
+    <col min="6658" max="6658" width="21.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="6659" max="6659" width="14.875" style="3" customWidth="1"/>
+    <col min="6660" max="6660" width="16.375" style="3" customWidth="1"/>
+    <col min="6661" max="6661" width="19.75" style="3" customWidth="1"/>
     <col min="6662" max="6913" width="9" style="3"/>
-    <col min="6914" max="6914" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="6915" max="6915" width="14.85546875" style="3" customWidth="1"/>
-    <col min="6916" max="6916" width="16.42578125" style="3" customWidth="1"/>
-    <col min="6917" max="6917" width="19.7109375" style="3" customWidth="1"/>
+    <col min="6914" max="6914" width="21.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="6915" max="6915" width="14.875" style="3" customWidth="1"/>
+    <col min="6916" max="6916" width="16.375" style="3" customWidth="1"/>
+    <col min="6917" max="6917" width="19.75" style="3" customWidth="1"/>
     <col min="6918" max="7169" width="9" style="3"/>
-    <col min="7170" max="7170" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="7171" max="7171" width="14.85546875" style="3" customWidth="1"/>
-    <col min="7172" max="7172" width="16.42578125" style="3" customWidth="1"/>
-    <col min="7173" max="7173" width="19.7109375" style="3" customWidth="1"/>
+    <col min="7170" max="7170" width="21.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="7171" max="7171" width="14.875" style="3" customWidth="1"/>
+    <col min="7172" max="7172" width="16.375" style="3" customWidth="1"/>
+    <col min="7173" max="7173" width="19.75" style="3" customWidth="1"/>
     <col min="7174" max="7425" width="9" style="3"/>
-    <col min="7426" max="7426" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="7427" max="7427" width="14.85546875" style="3" customWidth="1"/>
-    <col min="7428" max="7428" width="16.42578125" style="3" customWidth="1"/>
-    <col min="7429" max="7429" width="19.7109375" style="3" customWidth="1"/>
+    <col min="7426" max="7426" width="21.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="7427" max="7427" width="14.875" style="3" customWidth="1"/>
+    <col min="7428" max="7428" width="16.375" style="3" customWidth="1"/>
+    <col min="7429" max="7429" width="19.75" style="3" customWidth="1"/>
     <col min="7430" max="7681" width="9" style="3"/>
-    <col min="7682" max="7682" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="7683" max="7683" width="14.85546875" style="3" customWidth="1"/>
-    <col min="7684" max="7684" width="16.42578125" style="3" customWidth="1"/>
-    <col min="7685" max="7685" width="19.7109375" style="3" customWidth="1"/>
+    <col min="7682" max="7682" width="21.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="7683" max="7683" width="14.875" style="3" customWidth="1"/>
+    <col min="7684" max="7684" width="16.375" style="3" customWidth="1"/>
+    <col min="7685" max="7685" width="19.75" style="3" customWidth="1"/>
     <col min="7686" max="7937" width="9" style="3"/>
-    <col min="7938" max="7938" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="7939" max="7939" width="14.85546875" style="3" customWidth="1"/>
-    <col min="7940" max="7940" width="16.42578125" style="3" customWidth="1"/>
-    <col min="7941" max="7941" width="19.7109375" style="3" customWidth="1"/>
+    <col min="7938" max="7938" width="21.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="7939" max="7939" width="14.875" style="3" customWidth="1"/>
+    <col min="7940" max="7940" width="16.375" style="3" customWidth="1"/>
+    <col min="7941" max="7941" width="19.75" style="3" customWidth="1"/>
     <col min="7942" max="8193" width="9" style="3"/>
-    <col min="8194" max="8194" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="8195" max="8195" width="14.85546875" style="3" customWidth="1"/>
-    <col min="8196" max="8196" width="16.42578125" style="3" customWidth="1"/>
-    <col min="8197" max="8197" width="19.7109375" style="3" customWidth="1"/>
+    <col min="8194" max="8194" width="21.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="8195" max="8195" width="14.875" style="3" customWidth="1"/>
+    <col min="8196" max="8196" width="16.375" style="3" customWidth="1"/>
+    <col min="8197" max="8197" width="19.75" style="3" customWidth="1"/>
     <col min="8198" max="8449" width="9" style="3"/>
-    <col min="8450" max="8450" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="8451" max="8451" width="14.85546875" style="3" customWidth="1"/>
-    <col min="8452" max="8452" width="16.42578125" style="3" customWidth="1"/>
-    <col min="8453" max="8453" width="19.7109375" style="3" customWidth="1"/>
+    <col min="8450" max="8450" width="21.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="8451" max="8451" width="14.875" style="3" customWidth="1"/>
+    <col min="8452" max="8452" width="16.375" style="3" customWidth="1"/>
+    <col min="8453" max="8453" width="19.75" style="3" customWidth="1"/>
     <col min="8454" max="8705" width="9" style="3"/>
-    <col min="8706" max="8706" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="8707" max="8707" width="14.85546875" style="3" customWidth="1"/>
-    <col min="8708" max="8708" width="16.42578125" style="3" customWidth="1"/>
-    <col min="8709" max="8709" width="19.7109375" style="3" customWidth="1"/>
+    <col min="8706" max="8706" width="21.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="8707" max="8707" width="14.875" style="3" customWidth="1"/>
+    <col min="8708" max="8708" width="16.375" style="3" customWidth="1"/>
+    <col min="8709" max="8709" width="19.75" style="3" customWidth="1"/>
     <col min="8710" max="8961" width="9" style="3"/>
-    <col min="8962" max="8962" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="8963" max="8963" width="14.85546875" style="3" customWidth="1"/>
-    <col min="8964" max="8964" width="16.42578125" style="3" customWidth="1"/>
-    <col min="8965" max="8965" width="19.7109375" style="3" customWidth="1"/>
+    <col min="8962" max="8962" width="21.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="8963" max="8963" width="14.875" style="3" customWidth="1"/>
+    <col min="8964" max="8964" width="16.375" style="3" customWidth="1"/>
+    <col min="8965" max="8965" width="19.75" style="3" customWidth="1"/>
     <col min="8966" max="9217" width="9" style="3"/>
-    <col min="9218" max="9218" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="9219" max="9219" width="14.85546875" style="3" customWidth="1"/>
-    <col min="9220" max="9220" width="16.42578125" style="3" customWidth="1"/>
-    <col min="9221" max="9221" width="19.7109375" style="3" customWidth="1"/>
+    <col min="9218" max="9218" width="21.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="9219" max="9219" width="14.875" style="3" customWidth="1"/>
+    <col min="9220" max="9220" width="16.375" style="3" customWidth="1"/>
+    <col min="9221" max="9221" width="19.75" style="3" customWidth="1"/>
     <col min="9222" max="9473" width="9" style="3"/>
-    <col min="9474" max="9474" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="9475" max="9475" width="14.85546875" style="3" customWidth="1"/>
-    <col min="9476" max="9476" width="16.42578125" style="3" customWidth="1"/>
-    <col min="9477" max="9477" width="19.7109375" style="3" customWidth="1"/>
+    <col min="9474" max="9474" width="21.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="9475" max="9475" width="14.875" style="3" customWidth="1"/>
+    <col min="9476" max="9476" width="16.375" style="3" customWidth="1"/>
+    <col min="9477" max="9477" width="19.75" style="3" customWidth="1"/>
     <col min="9478" max="9729" width="9" style="3"/>
-    <col min="9730" max="9730" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="9731" max="9731" width="14.85546875" style="3" customWidth="1"/>
-    <col min="9732" max="9732" width="16.42578125" style="3" customWidth="1"/>
-    <col min="9733" max="9733" width="19.7109375" style="3" customWidth="1"/>
+    <col min="9730" max="9730" width="21.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="9731" max="9731" width="14.875" style="3" customWidth="1"/>
+    <col min="9732" max="9732" width="16.375" style="3" customWidth="1"/>
+    <col min="9733" max="9733" width="19.75" style="3" customWidth="1"/>
     <col min="9734" max="9985" width="9" style="3"/>
-    <col min="9986" max="9986" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="9987" max="9987" width="14.85546875" style="3" customWidth="1"/>
-    <col min="9988" max="9988" width="16.42578125" style="3" customWidth="1"/>
-    <col min="9989" max="9989" width="19.7109375" style="3" customWidth="1"/>
+    <col min="9986" max="9986" width="21.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="9987" max="9987" width="14.875" style="3" customWidth="1"/>
+    <col min="9988" max="9988" width="16.375" style="3" customWidth="1"/>
+    <col min="9989" max="9989" width="19.75" style="3" customWidth="1"/>
     <col min="9990" max="10241" width="9" style="3"/>
-    <col min="10242" max="10242" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="10243" max="10243" width="14.85546875" style="3" customWidth="1"/>
-    <col min="10244" max="10244" width="16.42578125" style="3" customWidth="1"/>
-    <col min="10245" max="10245" width="19.7109375" style="3" customWidth="1"/>
+    <col min="10242" max="10242" width="21.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="10243" max="10243" width="14.875" style="3" customWidth="1"/>
+    <col min="10244" max="10244" width="16.375" style="3" customWidth="1"/>
+    <col min="10245" max="10245" width="19.75" style="3" customWidth="1"/>
     <col min="10246" max="10497" width="9" style="3"/>
-    <col min="10498" max="10498" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="10499" max="10499" width="14.85546875" style="3" customWidth="1"/>
-    <col min="10500" max="10500" width="16.42578125" style="3" customWidth="1"/>
-    <col min="10501" max="10501" width="19.7109375" style="3" customWidth="1"/>
+    <col min="10498" max="10498" width="21.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="10499" max="10499" width="14.875" style="3" customWidth="1"/>
+    <col min="10500" max="10500" width="16.375" style="3" customWidth="1"/>
+    <col min="10501" max="10501" width="19.75" style="3" customWidth="1"/>
     <col min="10502" max="10753" width="9" style="3"/>
-    <col min="10754" max="10754" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="10755" max="10755" width="14.85546875" style="3" customWidth="1"/>
-    <col min="10756" max="10756" width="16.42578125" style="3" customWidth="1"/>
-    <col min="10757" max="10757" width="19.7109375" style="3" customWidth="1"/>
+    <col min="10754" max="10754" width="21.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="10755" max="10755" width="14.875" style="3" customWidth="1"/>
+    <col min="10756" max="10756" width="16.375" style="3" customWidth="1"/>
+    <col min="10757" max="10757" width="19.75" style="3" customWidth="1"/>
     <col min="10758" max="11009" width="9" style="3"/>
-    <col min="11010" max="11010" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="11011" max="11011" width="14.85546875" style="3" customWidth="1"/>
-    <col min="11012" max="11012" width="16.42578125" style="3" customWidth="1"/>
-    <col min="11013" max="11013" width="19.7109375" style="3" customWidth="1"/>
+    <col min="11010" max="11010" width="21.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="11011" max="11011" width="14.875" style="3" customWidth="1"/>
+    <col min="11012" max="11012" width="16.375" style="3" customWidth="1"/>
+    <col min="11013" max="11013" width="19.75" style="3" customWidth="1"/>
     <col min="11014" max="11265" width="9" style="3"/>
-    <col min="11266" max="11266" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="11267" max="11267" width="14.85546875" style="3" customWidth="1"/>
-    <col min="11268" max="11268" width="16.42578125" style="3" customWidth="1"/>
-    <col min="11269" max="11269" width="19.7109375" style="3" customWidth="1"/>
+    <col min="11266" max="11266" width="21.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="11267" max="11267" width="14.875" style="3" customWidth="1"/>
+    <col min="11268" max="11268" width="16.375" style="3" customWidth="1"/>
+    <col min="11269" max="11269" width="19.75" style="3" customWidth="1"/>
     <col min="11270" max="11521" width="9" style="3"/>
-    <col min="11522" max="11522" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="11523" max="11523" width="14.85546875" style="3" customWidth="1"/>
-    <col min="11524" max="11524" width="16.42578125" style="3" customWidth="1"/>
-    <col min="11525" max="11525" width="19.7109375" style="3" customWidth="1"/>
+    <col min="11522" max="11522" width="21.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="11523" max="11523" width="14.875" style="3" customWidth="1"/>
+    <col min="11524" max="11524" width="16.375" style="3" customWidth="1"/>
+    <col min="11525" max="11525" width="19.75" style="3" customWidth="1"/>
     <col min="11526" max="11777" width="9" style="3"/>
-    <col min="11778" max="11778" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="11779" max="11779" width="14.85546875" style="3" customWidth="1"/>
-    <col min="11780" max="11780" width="16.42578125" style="3" customWidth="1"/>
-    <col min="11781" max="11781" width="19.7109375" style="3" customWidth="1"/>
+    <col min="11778" max="11778" width="21.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="11779" max="11779" width="14.875" style="3" customWidth="1"/>
+    <col min="11780" max="11780" width="16.375" style="3" customWidth="1"/>
+    <col min="11781" max="11781" width="19.75" style="3" customWidth="1"/>
     <col min="11782" max="12033" width="9" style="3"/>
-    <col min="12034" max="12034" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="12035" max="12035" width="14.85546875" style="3" customWidth="1"/>
-    <col min="12036" max="12036" width="16.42578125" style="3" customWidth="1"/>
-    <col min="12037" max="12037" width="19.7109375" style="3" customWidth="1"/>
+    <col min="12034" max="12034" width="21.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="12035" max="12035" width="14.875" style="3" customWidth="1"/>
+    <col min="12036" max="12036" width="16.375" style="3" customWidth="1"/>
+    <col min="12037" max="12037" width="19.75" style="3" customWidth="1"/>
     <col min="12038" max="12289" width="9" style="3"/>
-    <col min="12290" max="12290" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="12291" max="12291" width="14.85546875" style="3" customWidth="1"/>
-    <col min="12292" max="12292" width="16.42578125" style="3" customWidth="1"/>
-    <col min="12293" max="12293" width="19.7109375" style="3" customWidth="1"/>
+    <col min="12290" max="12290" width="21.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="12291" max="12291" width="14.875" style="3" customWidth="1"/>
+    <col min="12292" max="12292" width="16.375" style="3" customWidth="1"/>
+    <col min="12293" max="12293" width="19.75" style="3" customWidth="1"/>
     <col min="12294" max="12545" width="9" style="3"/>
-    <col min="12546" max="12546" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="12547" max="12547" width="14.85546875" style="3" customWidth="1"/>
-    <col min="12548" max="12548" width="16.42578125" style="3" customWidth="1"/>
-    <col min="12549" max="12549" width="19.7109375" style="3" customWidth="1"/>
+    <col min="12546" max="12546" width="21.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="12547" max="12547" width="14.875" style="3" customWidth="1"/>
+    <col min="12548" max="12548" width="16.375" style="3" customWidth="1"/>
+    <col min="12549" max="12549" width="19.75" style="3" customWidth="1"/>
     <col min="12550" max="12801" width="9" style="3"/>
-    <col min="12802" max="12802" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="12803" max="12803" width="14.85546875" style="3" customWidth="1"/>
-    <col min="12804" max="12804" width="16.42578125" style="3" customWidth="1"/>
-    <col min="12805" max="12805" width="19.7109375" style="3" customWidth="1"/>
+    <col min="12802" max="12802" width="21.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="12803" max="12803" width="14.875" style="3" customWidth="1"/>
+    <col min="12804" max="12804" width="16.375" style="3" customWidth="1"/>
+    <col min="12805" max="12805" width="19.75" style="3" customWidth="1"/>
     <col min="12806" max="13057" width="9" style="3"/>
-    <col min="13058" max="13058" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="13059" max="13059" width="14.85546875" style="3" customWidth="1"/>
-    <col min="13060" max="13060" width="16.42578125" style="3" customWidth="1"/>
-    <col min="13061" max="13061" width="19.7109375" style="3" customWidth="1"/>
+    <col min="13058" max="13058" width="21.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="13059" max="13059" width="14.875" style="3" customWidth="1"/>
+    <col min="13060" max="13060" width="16.375" style="3" customWidth="1"/>
+    <col min="13061" max="13061" width="19.75" style="3" customWidth="1"/>
     <col min="13062" max="13313" width="9" style="3"/>
-    <col min="13314" max="13314" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="13315" max="13315" width="14.85546875" style="3" customWidth="1"/>
-    <col min="13316" max="13316" width="16.42578125" style="3" customWidth="1"/>
-    <col min="13317" max="13317" width="19.7109375" style="3" customWidth="1"/>
+    <col min="13314" max="13314" width="21.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="13315" max="13315" width="14.875" style="3" customWidth="1"/>
+    <col min="13316" max="13316" width="16.375" style="3" customWidth="1"/>
+    <col min="13317" max="13317" width="19.75" style="3" customWidth="1"/>
     <col min="13318" max="13569" width="9" style="3"/>
-    <col min="13570" max="13570" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="13571" max="13571" width="14.85546875" style="3" customWidth="1"/>
-    <col min="13572" max="13572" width="16.42578125" style="3" customWidth="1"/>
-    <col min="13573" max="13573" width="19.7109375" style="3" customWidth="1"/>
+    <col min="13570" max="13570" width="21.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="13571" max="13571" width="14.875" style="3" customWidth="1"/>
+    <col min="13572" max="13572" width="16.375" style="3" customWidth="1"/>
+    <col min="13573" max="13573" width="19.75" style="3" customWidth="1"/>
     <col min="13574" max="13825" width="9" style="3"/>
-    <col min="13826" max="13826" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="13827" max="13827" width="14.85546875" style="3" customWidth="1"/>
-    <col min="13828" max="13828" width="16.42578125" style="3" customWidth="1"/>
-    <col min="13829" max="13829" width="19.7109375" style="3" customWidth="1"/>
+    <col min="13826" max="13826" width="21.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="13827" max="13827" width="14.875" style="3" customWidth="1"/>
+    <col min="13828" max="13828" width="16.375" style="3" customWidth="1"/>
+    <col min="13829" max="13829" width="19.75" style="3" customWidth="1"/>
     <col min="13830" max="14081" width="9" style="3"/>
-    <col min="14082" max="14082" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="14083" max="14083" width="14.85546875" style="3" customWidth="1"/>
-    <col min="14084" max="14084" width="16.42578125" style="3" customWidth="1"/>
-    <col min="14085" max="14085" width="19.7109375" style="3" customWidth="1"/>
+    <col min="14082" max="14082" width="21.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="14083" max="14083" width="14.875" style="3" customWidth="1"/>
+    <col min="14084" max="14084" width="16.375" style="3" customWidth="1"/>
+    <col min="14085" max="14085" width="19.75" style="3" customWidth="1"/>
     <col min="14086" max="14337" width="9" style="3"/>
-    <col min="14338" max="14338" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="14339" max="14339" width="14.85546875" style="3" customWidth="1"/>
-    <col min="14340" max="14340" width="16.42578125" style="3" customWidth="1"/>
-    <col min="14341" max="14341" width="19.7109375" style="3" customWidth="1"/>
+    <col min="14338" max="14338" width="21.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="14339" max="14339" width="14.875" style="3" customWidth="1"/>
+    <col min="14340" max="14340" width="16.375" style="3" customWidth="1"/>
+    <col min="14341" max="14341" width="19.75" style="3" customWidth="1"/>
     <col min="14342" max="14593" width="9" style="3"/>
-    <col min="14594" max="14594" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="14595" max="14595" width="14.85546875" style="3" customWidth="1"/>
-    <col min="14596" max="14596" width="16.42578125" style="3" customWidth="1"/>
-    <col min="14597" max="14597" width="19.7109375" style="3" customWidth="1"/>
+    <col min="14594" max="14594" width="21.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="14595" max="14595" width="14.875" style="3" customWidth="1"/>
+    <col min="14596" max="14596" width="16.375" style="3" customWidth="1"/>
+    <col min="14597" max="14597" width="19.75" style="3" customWidth="1"/>
     <col min="14598" max="14849" width="9" style="3"/>
-    <col min="14850" max="14850" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="14851" max="14851" width="14.85546875" style="3" customWidth="1"/>
-    <col min="14852" max="14852" width="16.42578125" style="3" customWidth="1"/>
-    <col min="14853" max="14853" width="19.7109375" style="3" customWidth="1"/>
+    <col min="14850" max="14850" width="21.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="14851" max="14851" width="14.875" style="3" customWidth="1"/>
+    <col min="14852" max="14852" width="16.375" style="3" customWidth="1"/>
+    <col min="14853" max="14853" width="19.75" style="3" customWidth="1"/>
     <col min="14854" max="15105" width="9" style="3"/>
-    <col min="15106" max="15106" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="15107" max="15107" width="14.85546875" style="3" customWidth="1"/>
-    <col min="15108" max="15108" width="16.42578125" style="3" customWidth="1"/>
-    <col min="15109" max="15109" width="19.7109375" style="3" customWidth="1"/>
+    <col min="15106" max="15106" width="21.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="15107" max="15107" width="14.875" style="3" customWidth="1"/>
+    <col min="15108" max="15108" width="16.375" style="3" customWidth="1"/>
+    <col min="15109" max="15109" width="19.75" style="3" customWidth="1"/>
     <col min="15110" max="15361" width="9" style="3"/>
-    <col min="15362" max="15362" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="15363" max="15363" width="14.85546875" style="3" customWidth="1"/>
-    <col min="15364" max="15364" width="16.42578125" style="3" customWidth="1"/>
-    <col min="15365" max="15365" width="19.7109375" style="3" customWidth="1"/>
+    <col min="15362" max="15362" width="21.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="15363" max="15363" width="14.875" style="3" customWidth="1"/>
+    <col min="15364" max="15364" width="16.375" style="3" customWidth="1"/>
+    <col min="15365" max="15365" width="19.75" style="3" customWidth="1"/>
     <col min="15366" max="15617" width="9" style="3"/>
-    <col min="15618" max="15618" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="15619" max="15619" width="14.85546875" style="3" customWidth="1"/>
-    <col min="15620" max="15620" width="16.42578125" style="3" customWidth="1"/>
-    <col min="15621" max="15621" width="19.7109375" style="3" customWidth="1"/>
+    <col min="15618" max="15618" width="21.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="15619" max="15619" width="14.875" style="3" customWidth="1"/>
+    <col min="15620" max="15620" width="16.375" style="3" customWidth="1"/>
+    <col min="15621" max="15621" width="19.75" style="3" customWidth="1"/>
     <col min="15622" max="15873" width="9" style="3"/>
-    <col min="15874" max="15874" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="15875" max="15875" width="14.85546875" style="3" customWidth="1"/>
-    <col min="15876" max="15876" width="16.42578125" style="3" customWidth="1"/>
-    <col min="15877" max="15877" width="19.7109375" style="3" customWidth="1"/>
+    <col min="15874" max="15874" width="21.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="15875" max="15875" width="14.875" style="3" customWidth="1"/>
+    <col min="15876" max="15876" width="16.375" style="3" customWidth="1"/>
+    <col min="15877" max="15877" width="19.75" style="3" customWidth="1"/>
     <col min="15878" max="16129" width="9" style="3"/>
-    <col min="16130" max="16130" width="21.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="16131" max="16131" width="14.85546875" style="3" customWidth="1"/>
-    <col min="16132" max="16132" width="16.42578125" style="3" customWidth="1"/>
-    <col min="16133" max="16133" width="19.7109375" style="3" customWidth="1"/>
+    <col min="16130" max="16130" width="21.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="16131" max="16131" width="14.875" style="3" customWidth="1"/>
+    <col min="16132" max="16132" width="16.375" style="3" customWidth="1"/>
+    <col min="16133" max="16133" width="19.75" style="3" customWidth="1"/>
     <col min="16134" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="20.25">
+    <row r="1" spans="1:5" ht="21" x14ac:dyDescent="0.3">
       <c r="A1" s="15" t="s">
         <v>14</v>
       </c>
@@ -2423,14 +2456,14 @@
       <c r="D1" s="15"/>
       <c r="E1" s="15"/>
     </row>
-    <row r="2" spans="1:5" ht="20.25">
+    <row r="2" spans="1:5" ht="21" x14ac:dyDescent="0.3">
       <c r="A2" s="4"/>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>15</v>
       </c>
@@ -2447,7 +2480,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="6">
         <v>1</v>
       </c>
@@ -2456,7 +2489,7 @@
       <c r="D5" s="6"/>
       <c r="E5" s="6"/>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="6">
         <v>2</v>
       </c>
@@ -2465,7 +2498,7 @@
       <c r="D6" s="6"/>
       <c r="E6" s="6"/>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="6">
         <v>3</v>
       </c>
@@ -2474,175 +2507,175 @@
       <c r="D7" s="6"/>
       <c r="E7" s="6"/>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="6"/>
       <c r="B8" s="6"/>
       <c r="C8" s="6"/>
       <c r="D8" s="6"/>
       <c r="E8" s="6"/>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="6"/>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
       <c r="D9" s="6"/>
       <c r="E9" s="6"/>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="6"/>
       <c r="B10" s="6"/>
       <c r="C10" s="6"/>
       <c r="D10" s="6"/>
       <c r="E10" s="6"/>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="6"/>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
       <c r="D11" s="6"/>
       <c r="E11" s="6"/>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="6"/>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
       <c r="D12" s="6"/>
       <c r="E12" s="6"/>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="6"/>
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
       <c r="E13" s="6"/>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="6"/>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
       <c r="D14" s="6"/>
       <c r="E14" s="6"/>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="6"/>
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
       <c r="E15" s="6"/>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="6"/>
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
       <c r="D16" s="6"/>
       <c r="E16" s="6"/>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="6"/>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
       <c r="D17" s="6"/>
       <c r="E17" s="6"/>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="6"/>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
       <c r="D18" s="6"/>
       <c r="E18" s="6"/>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="6"/>
       <c r="B19" s="6"/>
       <c r="C19" s="6"/>
       <c r="D19" s="6"/>
       <c r="E19" s="6"/>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="6"/>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
       <c r="D20" s="6"/>
       <c r="E20" s="6"/>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="6"/>
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
       <c r="D21" s="6"/>
       <c r="E21" s="6"/>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="6"/>
       <c r="B22" s="6"/>
       <c r="C22" s="6"/>
       <c r="D22" s="6"/>
       <c r="E22" s="6"/>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="6"/>
       <c r="B23" s="6"/>
       <c r="C23" s="6"/>
       <c r="D23" s="6"/>
       <c r="E23" s="6"/>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="6"/>
       <c r="B24" s="6"/>
       <c r="C24" s="6"/>
       <c r="D24" s="6"/>
       <c r="E24" s="6"/>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="6"/>
       <c r="B25" s="6"/>
       <c r="C25" s="6"/>
       <c r="D25" s="6"/>
       <c r="E25" s="6"/>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="6"/>
       <c r="B26" s="6"/>
       <c r="C26" s="6"/>
       <c r="D26" s="6"/>
       <c r="E26" s="6"/>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="6"/>
       <c r="B27" s="6"/>
       <c r="C27" s="6"/>
       <c r="D27" s="6"/>
       <c r="E27" s="6"/>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="6"/>
       <c r="B28" s="6"/>
       <c r="C28" s="6"/>
       <c r="D28" s="6"/>
       <c r="E28" s="6"/>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="6"/>
       <c r="B29" s="6"/>
       <c r="C29" s="6"/>
       <c r="D29" s="6"/>
       <c r="E29" s="6"/>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="6"/>
       <c r="B30" s="6"/>
       <c r="C30" s="6"/>
       <c r="D30" s="6"/>
       <c r="E30" s="6"/>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="6"/>
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
       <c r="D31" s="6"/>
       <c r="E31" s="6"/>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="6"/>
       <c r="B32" s="6"/>
       <c r="C32" s="6"/>
